--- a/docs/assets/BoM.xlsx
+++ b/docs/assets/BoM.xlsx
@@ -132,7 +132,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -286,12 +286,56 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -374,6 +418,8 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -803,8 +849,8 @@
           <t>Circuit</t>
         </is>
       </c>
-      <c r="B2" s="45" t="n"/>
-      <c r="C2" s="45" t="n"/>
+      <c r="B2" s="64" t="n"/>
+      <c r="C2" s="65" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="46" t="inlineStr">
@@ -1011,8 +1057,8 @@
           <t>Mount</t>
         </is>
       </c>
-      <c r="B16" s="45" t="n"/>
-      <c r="C16" s="45" t="n"/>
+      <c r="B16" s="64" t="n"/>
+      <c r="C16" s="65" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="46" t="inlineStr">
@@ -1230,8 +1276,8 @@
           <t>Mount - HDMI</t>
         </is>
       </c>
-      <c r="B31" s="45" t="n"/>
-      <c r="C31" s="45" t="n"/>
+      <c r="B31" s="64" t="n"/>
+      <c r="C31" s="65" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="46" t="inlineStr">
@@ -1269,8 +1315,8 @@
           <t>Mount - SDI</t>
         </is>
       </c>
-      <c r="B34" s="45" t="n"/>
-      <c r="C34" s="45" t="n"/>
+      <c r="B34" s="64" t="n"/>
+      <c r="C34" s="65" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="46" t="inlineStr">
@@ -1308,8 +1354,8 @@
           <t>Mount - BMD Converter</t>
         </is>
       </c>
-      <c r="B37" s="45" t="n"/>
-      <c r="C37" s="45" t="n"/>
+      <c r="B37" s="64" t="n"/>
+      <c r="C37" s="65" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="46" t="inlineStr">
@@ -1377,8 +1423,8 @@
           <t>Slider</t>
         </is>
       </c>
-      <c r="B42" s="45" t="n"/>
-      <c r="C42" s="45" t="n"/>
+      <c r="B42" s="64" t="n"/>
+      <c r="C42" s="65" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="46" t="inlineStr">
@@ -1523,8 +1569,8 @@
           <t>Slider - HDMI</t>
         </is>
       </c>
-      <c r="B52" s="45" t="n"/>
-      <c r="C52" s="45" t="n"/>
+      <c r="B52" s="64" t="n"/>
+      <c r="C52" s="65" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="46" t="inlineStr">
@@ -1562,8 +1608,8 @@
           <t>Slider - SDI</t>
         </is>
       </c>
-      <c r="B55" s="45" t="n"/>
-      <c r="C55" s="45" t="n"/>
+      <c r="B55" s="64" t="n"/>
+      <c r="C55" s="65" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="46" t="inlineStr">
@@ -1601,8 +1647,8 @@
           <t>Slider - BMD Converter</t>
         </is>
       </c>
-      <c r="B58" s="45" t="n"/>
-      <c r="C58" s="45" t="n"/>
+      <c r="B58" s="64" t="n"/>
+      <c r="C58" s="65" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="46" t="inlineStr">
@@ -1640,8 +1686,8 @@
           <t>Hub</t>
         </is>
       </c>
-      <c r="B61" s="45" t="n"/>
-      <c r="C61" s="45" t="n"/>
+      <c r="B61" s="64" t="n"/>
+      <c r="C61" s="65" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="46" t="inlineStr">
@@ -1664,8 +1710,8 @@
           <t>Hub Display</t>
         </is>
       </c>
-      <c r="B63" s="45" t="n"/>
-      <c r="C63" s="45" t="n"/>
+      <c r="B63" s="64" t="n"/>
+      <c r="C63" s="65" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="46" t="inlineStr">
@@ -1733,8 +1779,8 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="B68" s="45" t="n"/>
-      <c r="C68" s="45" t="n"/>
+      <c r="B68" s="64" t="n"/>
+      <c r="C68" s="65" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="46" t="inlineStr">
@@ -1772,8 +1818,8 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="B71" s="45" t="n"/>
-      <c r="C71" s="45" t="n"/>
+      <c r="B71" s="64" t="n"/>
+      <c r="C71" s="65" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="46" t="inlineStr">
@@ -1876,7 +1922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS57"/>
+  <dimension ref="A1:AN57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="10.83203125" customWidth="1" style="19" min="1" max="1"/>
@@ -2966,7 +3012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V34"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="3.33203125" customWidth="1" min="1" max="1"/>
@@ -4092,35 +4138,6 @@
         <v/>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="62" t="inlineStr">
-        <is>
-          <t>M8 Washer</t>
-        </is>
-      </c>
-      <c r="C34" s="47" t="n"/>
-      <c r="D34" s="47" t="n"/>
-      <c r="E34" s="47" t="n"/>
-      <c r="F34" s="47" t="n"/>
-      <c r="G34" s="47" t="n"/>
-      <c r="H34" s="47" t="n"/>
-      <c r="I34" s="47" t="n"/>
-      <c r="J34" s="47" t="n"/>
-      <c r="K34" s="47" t="n"/>
-      <c r="L34" s="47" t="n"/>
-      <c r="M34" s="47" t="n"/>
-      <c r="N34" s="47" t="n"/>
-      <c r="O34" s="47" t="n"/>
-      <c r="P34" s="47" t="n"/>
-      <c r="Q34" s="47" t="n"/>
-      <c r="R34" s="47" t="n"/>
-      <c r="S34" s="47" t="n"/>
-      <c r="T34" s="47" t="n"/>
-      <c r="U34" s="63">
-        <f>SUM(C34:T34)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/assets/BoM.xlsx
+++ b/docs/assets/BoM.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="800" windowWidth="36000" windowHeight="22580" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="800" windowWidth="36000" windowHeight="22580" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Parts" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="17">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -39,36 +39,21 @@
       <sz val="12"/>
     </font>
     <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color theme="10"/>
-      <sz val="12"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="Helvetica Neue"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001F3864"/>
+      <color rgb="FF1F3864"/>
       <sz val="10"/>
     </font>
     <font>
@@ -77,14 +62,14 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="000563C1"/>
+      <color rgb="FF0563C1"/>
       <sz val="10"/>
       <u val="single"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
@@ -99,8 +84,38 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001F3864"/>
+      <color rgb="FF1F3864"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1F3864"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -118,21 +133,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F5597"/>
+        <fgColor rgb="FF2F5597"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
+        <fgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -221,21 +236,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -274,23 +274,48 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -298,132 +323,92 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -819,7 +804,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C72"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
@@ -827,1010 +812,1010 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="42" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="43" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="C1" s="43" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>Buy</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="44" t="inlineStr">
+      <c r="A2" s="33" t="inlineStr">
         <is>
           <t>Circuit</t>
         </is>
       </c>
-      <c r="B2" s="64" t="n"/>
-      <c r="C2" s="65" t="n"/>
+      <c r="B2" s="34" t="n"/>
+      <c r="C2" s="35" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="46" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Teensy 4.1</t>
         </is>
       </c>
-      <c r="B3" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="48" t="inlineStr">
+      <c r="B3" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="46" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>TMC2209</t>
         </is>
       </c>
-      <c r="B4" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="C4" s="48" t="inlineStr">
+      <c r="B4" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="46" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>5V regulator</t>
         </is>
       </c>
-      <c r="B5" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="48" t="inlineStr">
+      <c r="B5" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="46" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>1n4007</t>
         </is>
       </c>
-      <c r="B6" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="48" t="inlineStr">
+      <c r="B6" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="46" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>100nf 35v</t>
         </is>
       </c>
-      <c r="B7" s="47" t="n">
+      <c r="B7" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="48" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="46" t="inlineStr">
-        <is>
-          <t>10K ¼W</t>
-        </is>
-      </c>
-      <c r="B8" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="48" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
+        <is>
+          <t>1K ¼W</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="46" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>100K ¼W</t>
         </is>
       </c>
-      <c r="B9" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="48" t="inlineStr">
+      <c r="B9" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="46" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Screw PCB terminals 5.08mm 2pin</t>
         </is>
       </c>
-      <c r="B10" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="48" t="inlineStr">
+      <c r="B10" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="46" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>JST 4pin Plug + Lead + Socket</t>
         </is>
       </c>
-      <c r="B11" s="47" t="n">
+      <c r="B11" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="C11" s="48" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="46" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>JST 5pin Plug + Lead + Socket</t>
         </is>
       </c>
-      <c r="B12" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="48" t="inlineStr">
+      <c r="B12" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="46" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>JST 2pin Plug + Lead + Socket</t>
         </is>
       </c>
-      <c r="B13" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" s="48" t="inlineStr">
+      <c r="B13" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="46" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Header Sockets</t>
         </is>
       </c>
-      <c r="B14" s="47" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
       </c>
-      <c r="C14" s="48" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="46" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Header Pins</t>
         </is>
       </c>
-      <c r="B15" s="47" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
       </c>
-      <c r="C15" s="48" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="44" t="inlineStr">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>Mount</t>
         </is>
       </c>
-      <c r="B16" s="64" t="n"/>
-      <c r="C16" s="65" t="n"/>
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="35" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="46" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>6824ZZ 120x150x16mm Bearing</t>
         </is>
       </c>
-      <c r="B17" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="48" t="inlineStr">
+      <c r="B17" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>Simply Bearings</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="46" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>F688ZZ Flanged Bearing 8 x 16 x 5mm</t>
         </is>
       </c>
-      <c r="B18" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="C18" s="48" t="inlineStr">
+      <c r="B18" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="46" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>GT2 Pulley - 120 tooth, 8mm bore</t>
         </is>
       </c>
-      <c r="B19" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="48" t="inlineStr">
+      <c r="B19" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="46" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>GT2 Pulley - 36 tooth, 5mm bore</t>
         </is>
       </c>
-      <c r="B20" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="48" t="inlineStr">
+      <c r="B20" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="46" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>GT2 Pulley - 16 tooth, 5mm bore</t>
         </is>
       </c>
-      <c r="B21" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="48" t="inlineStr">
+      <c r="B21" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="46" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>GT2 Belt - 580mm loop, 6mm wide</t>
         </is>
       </c>
-      <c r="B22" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="48" t="inlineStr">
+      <c r="B22" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="46" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>GT2 Belt - 350mm loop, 6mm wide</t>
         </is>
       </c>
-      <c r="B23" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="48" t="inlineStr">
+      <c r="B23" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="46" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Nema14 0.9 deg 36Ncm</t>
         </is>
       </c>
-      <c r="B24" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="C24" s="48" t="inlineStr">
+      <c r="B24" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="46" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Nema14 Round Pancake Stepper Motor 0.9 deg</t>
         </is>
       </c>
-      <c r="B25" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="48" t="inlineStr">
+      <c r="B25" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="46" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>GX12 2 Pin Aviation Connector &amp; Panel Socket</t>
         </is>
       </c>
-      <c r="B26" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="48" t="inlineStr">
+      <c r="B26" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="46" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Waveshare ESP32-S3 1.75inch AMOLED Round Touch Display</t>
         </is>
       </c>
-      <c r="B27" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="48" t="inlineStr">
+      <c r="B27" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="46" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Sticky Pads Heavy Duty 40x40mm</t>
         </is>
       </c>
-      <c r="B28" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="48" t="inlineStr">
+      <c r="B28" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="46" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>2.4GHz Antenna</t>
         </is>
       </c>
-      <c r="B29" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="48" t="inlineStr">
+      <c r="B29" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="46" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>U.FL Mini PCI to SMA Female 20cm Lead</t>
         </is>
       </c>
-      <c r="B30" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="48" t="inlineStr">
+      <c r="B30" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="44" t="inlineStr">
+      <c r="A31" s="33" t="inlineStr">
         <is>
           <t>Mount - HDMI</t>
         </is>
       </c>
-      <c r="B31" s="64" t="n"/>
-      <c r="C31" s="65" t="n"/>
+      <c r="B31" s="34" t="n"/>
+      <c r="C31" s="35" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="46" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>HDMI Keystone coupler</t>
         </is>
       </c>
-      <c r="B32" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" s="48" t="inlineStr">
+      <c r="B32" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="46" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>HDMI Cable - 1m</t>
         </is>
       </c>
-      <c r="B33" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="48" t="inlineStr">
+      <c r="B33" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="44" t="inlineStr">
+      <c r="A34" s="33" t="inlineStr">
         <is>
           <t>Mount - SDI</t>
         </is>
       </c>
-      <c r="B34" s="64" t="n"/>
-      <c r="C34" s="65" t="n"/>
+      <c r="B34" s="34" t="n"/>
+      <c r="C34" s="35" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="46" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>SDI Panel mount coupler</t>
         </is>
       </c>
-      <c r="B35" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="48" t="inlineStr">
+      <c r="B35" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="46" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>HD-SDI Cable - 1m</t>
         </is>
       </c>
-      <c r="B36" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="48" t="inlineStr">
+      <c r="B36" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="44" t="inlineStr">
+      <c r="A37" s="33" t="inlineStr">
         <is>
           <t>Mount - BMD Converter</t>
         </is>
       </c>
-      <c r="B37" s="64" t="n"/>
-      <c r="C37" s="65" t="n"/>
+      <c r="B37" s="34" t="n"/>
+      <c r="C37" s="35" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="46" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>Blackmagic Design Bi-Directional SDI/HDMI 3G</t>
         </is>
       </c>
-      <c r="B38" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="48" t="inlineStr">
+      <c r="B38" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="17" t="inlineStr">
         <is>
           <t>Thomann</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="46" t="inlineStr">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>SDI Panel mount coupler</t>
         </is>
       </c>
-      <c r="B39" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="C39" s="48" t="inlineStr">
+      <c r="B39" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="46" t="inlineStr">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>HD-SDI Cable - 1m, Right angle</t>
         </is>
       </c>
-      <c r="B40" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="C40" s="48" t="inlineStr">
+      <c r="B40" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="46" t="inlineStr">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>USB-C Cable - 1 Metre (cut and soldered to JST 2pin)</t>
         </is>
       </c>
-      <c r="B41" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" s="48" t="inlineStr">
+      <c r="B41" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="44" t="inlineStr">
+      <c r="A42" s="33" t="inlineStr">
         <is>
           <t>Slider</t>
         </is>
       </c>
-      <c r="B42" s="64" t="n"/>
-      <c r="C42" s="65" t="n"/>
+      <c r="B42" s="34" t="n"/>
+      <c r="C42" s="35" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="15" t="inlineStr">
         <is>
           <t>Aluminium Extrusion - 8040 C</t>
         </is>
       </c>
-      <c r="B43" s="47" t="inlineStr">
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>1000 - 3000mm</t>
         </is>
       </c>
-      <c r="C43" s="48" t="inlineStr">
+      <c r="C43" s="17" t="inlineStr">
         <is>
           <t>Ooznest</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="46" t="inlineStr">
+      <c r="A44" s="15" t="inlineStr">
         <is>
           <t>GT2 Pulley - 36 tooth</t>
         </is>
       </c>
-      <c r="B44" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" s="48" t="inlineStr">
+      <c r="B44" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>GT2 Belt - 5m</t>
         </is>
       </c>
-      <c r="B45" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" s="48" t="inlineStr">
+      <c r="B45" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="46" t="inlineStr">
+      <c r="A46" s="15" t="inlineStr">
         <is>
           <t>Idler - 6mm width, 3mm bore, 13mm diameter</t>
         </is>
       </c>
-      <c r="B46" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="C46" s="48" t="inlineStr">
+      <c r="B46" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="46" t="inlineStr">
+      <c r="A47" s="15" t="inlineStr">
         <is>
           <t>Nema14 1.8 deg 65Ncm</t>
         </is>
       </c>
-      <c r="B47" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" s="48" t="inlineStr">
+      <c r="B47" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="15" t="inlineStr">
         <is>
           <t>V Slot Pulley Wheels 625zz</t>
         </is>
       </c>
-      <c r="B48" s="47" t="n">
+      <c r="B48" s="16" t="n">
         <v>16</v>
       </c>
-      <c r="C48" s="48" t="inlineStr">
+      <c r="C48" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="46" t="inlineStr">
+      <c r="A49" s="15" t="inlineStr">
         <is>
           <t>XT60 Plug Connector Female and Male</t>
         </is>
       </c>
-      <c r="B49" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" s="48" t="inlineStr">
+      <c r="B49" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="46" t="inlineStr">
+      <c r="A50" s="15" t="inlineStr">
         <is>
           <t>GX12 2 Pin Aviation Connector &amp; Panel Socket</t>
         </is>
       </c>
-      <c r="B50" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" s="48" t="inlineStr">
+      <c r="B50" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="15" t="inlineStr">
         <is>
           <t>GX12 4 Pin Aviation Connector &amp; Panel Socket</t>
         </is>
       </c>
-      <c r="B51" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" s="48" t="inlineStr">
+      <c r="B51" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="44" t="inlineStr">
+      <c r="A52" s="33" t="inlineStr">
         <is>
           <t>Slider - HDMI</t>
         </is>
       </c>
-      <c r="B52" s="64" t="n"/>
-      <c r="C52" s="65" t="n"/>
+      <c r="B52" s="34" t="n"/>
+      <c r="C52" s="35" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="46" t="inlineStr">
+      <c r="A53" s="15" t="inlineStr">
         <is>
           <t>HDMI Keystone coupler</t>
         </is>
       </c>
-      <c r="B53" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" s="48" t="inlineStr">
+      <c r="B53" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="46" t="inlineStr">
+      <c r="A54" s="15" t="inlineStr">
         <is>
           <t>HDMI Cable, 2m - 4m</t>
         </is>
       </c>
-      <c r="B54" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" s="48" t="inlineStr">
+      <c r="B54" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="44" t="inlineStr">
+      <c r="A55" s="33" t="inlineStr">
         <is>
           <t>Slider - SDI</t>
         </is>
       </c>
-      <c r="B55" s="64" t="n"/>
-      <c r="C55" s="65" t="n"/>
+      <c r="B55" s="34" t="n"/>
+      <c r="C55" s="35" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="15" t="inlineStr">
         <is>
           <t>SDI Panel mount coupler</t>
         </is>
       </c>
-      <c r="B56" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" s="48" t="inlineStr">
+      <c r="B56" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="46" t="inlineStr">
+      <c r="A57" s="15" t="inlineStr">
         <is>
           <t>HD-SDI Cable, 1m - 4m</t>
         </is>
       </c>
-      <c r="B57" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" s="48" t="inlineStr">
+      <c r="B57" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="44" t="inlineStr">
+      <c r="A58" s="33" t="inlineStr">
         <is>
           <t>Slider - BMD Converter</t>
         </is>
       </c>
-      <c r="B58" s="64" t="n"/>
-      <c r="C58" s="65" t="n"/>
+      <c r="B58" s="34" t="n"/>
+      <c r="C58" s="35" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
+      <c r="A59" s="15" t="inlineStr">
         <is>
           <t>SDI Panel mount coupler</t>
         </is>
       </c>
-      <c r="B59" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="C59" s="48" t="inlineStr">
+      <c r="B59" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C59" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="46" t="inlineStr">
+      <c r="A60" s="15" t="inlineStr">
         <is>
           <t>HD-SDI Cable, 2m - 4m</t>
         </is>
       </c>
-      <c r="B60" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="C60" s="48" t="inlineStr">
+      <c r="B60" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C60" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="44" t="inlineStr">
+      <c r="A61" s="33" t="inlineStr">
         <is>
           <t>Hub</t>
         </is>
       </c>
-      <c r="B61" s="64" t="n"/>
-      <c r="C61" s="65" t="n"/>
+      <c r="B61" s="34" t="n"/>
+      <c r="C61" s="35" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="46" t="inlineStr">
+      <c r="A62" s="15" t="inlineStr">
         <is>
           <t>Seeed Studio XIAO ESP32S3</t>
         </is>
       </c>
-      <c r="B62" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C62" s="48" t="inlineStr">
+      <c r="B62" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="44" t="inlineStr">
+      <c r="A63" s="33" t="inlineStr">
         <is>
           <t>Hub Display</t>
         </is>
       </c>
-      <c r="B63" s="64" t="n"/>
-      <c r="C63" s="65" t="n"/>
+      <c r="B63" s="34" t="n"/>
+      <c r="C63" s="35" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="46" t="inlineStr">
+      <c r="A64" s="15" t="inlineStr">
         <is>
           <t>Waveshare ESP32-S3 7inch Capacitive Touch LCD</t>
         </is>
       </c>
-      <c r="B64" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C64" s="48" t="inlineStr">
+      <c r="B64" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="46" t="inlineStr">
+      <c r="A65" s="15" t="inlineStr">
         <is>
           <t>2.4GHz Antenna</t>
         </is>
       </c>
-      <c r="B65" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C65" s="48" t="inlineStr">
+      <c r="B65" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="46" t="inlineStr">
+      <c r="A66" s="15" t="inlineStr">
         <is>
           <t>U.FL Mini PCI to SMA Female 20cm Lead</t>
         </is>
       </c>
-      <c r="B66" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C66" s="48" t="inlineStr">
+      <c r="B66" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="46" t="inlineStr">
+      <c r="A67" s="15" t="inlineStr">
         <is>
           <t>USB-C Screw Hole Panel Mount</t>
         </is>
       </c>
-      <c r="B67" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C67" s="48" t="inlineStr">
+      <c r="B67" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="44" t="inlineStr">
+      <c r="A68" s="33" t="inlineStr">
         <is>
           <t>Misc</t>
         </is>
       </c>
-      <c r="B68" s="64" t="n"/>
-      <c r="C68" s="65" t="n"/>
+      <c r="B68" s="34" t="n"/>
+      <c r="C68" s="35" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="46" t="inlineStr">
+      <c r="A69" s="15" t="inlineStr">
         <is>
           <t>2 Core Wire - 30m, 20awg</t>
         </is>
       </c>
-      <c r="B69" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C69" s="48" t="inlineStr">
+      <c r="B69" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="46" t="inlineStr">
+      <c r="A70" s="15" t="inlineStr">
         <is>
           <t>4 Core Wire - 10m, 24awg</t>
         </is>
       </c>
-      <c r="B70" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C70" s="48" t="inlineStr">
+      <c r="B70" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="44" t="inlineStr">
+      <c r="A71" s="33" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="B71" s="64" t="n"/>
-      <c r="C71" s="65" t="n"/>
+      <c r="B71" s="34" t="n"/>
+      <c r="C71" s="35" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="46" t="inlineStr">
+      <c r="A72" s="15" t="inlineStr">
         <is>
           <t>UGREEN Video Capture Card HDMI to USB C 1080P 60FPS Capture (CV Tracking)</t>
         </is>
       </c>
-      <c r="B72" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C72" s="48" t="inlineStr">
+      <c r="B72" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
@@ -1922,1084 +1907,1123 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN57"/>
+  <dimension ref="B2:AN57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col width="10.83203125" customWidth="1" style="19" min="1" max="1"/>
-    <col width="24.1640625" customWidth="1" style="19" min="2" max="2"/>
-    <col width="3.1640625" customWidth="1" style="19" min="3" max="3"/>
-    <col width="11.83203125" customWidth="1" style="19" min="4" max="4"/>
-    <col width="10.83203125" customWidth="1" style="19" min="5" max="5"/>
-    <col width="17.1640625" customWidth="1" style="19" min="6" max="6"/>
-    <col width="3.33203125" customWidth="1" style="19" min="7" max="7"/>
-    <col width="11.5" customWidth="1" style="19" min="8" max="8"/>
-    <col width="10.83203125" customWidth="1" style="19" min="9" max="9"/>
-    <col width="15.5" customWidth="1" style="19" min="10" max="10"/>
-    <col width="3.5" customWidth="1" style="19" min="11" max="11"/>
-    <col width="18" customWidth="1" style="19" min="12" max="12"/>
-    <col width="10.83203125" customWidth="1" style="19" min="13" max="13"/>
-    <col width="22.33203125" customWidth="1" style="19" min="14" max="14"/>
-    <col width="5" customWidth="1" style="19" min="15" max="15"/>
-    <col width="16" customWidth="1" style="19" min="16" max="16"/>
-    <col width="10.83203125" customWidth="1" style="19" min="17" max="17"/>
-    <col width="15.83203125" customWidth="1" style="19" min="18" max="18"/>
-    <col width="2.83203125" customWidth="1" style="19" min="19" max="19"/>
-    <col width="10.83203125" customWidth="1" style="19" min="20" max="21"/>
-    <col width="18.83203125" customWidth="1" style="19" min="22" max="22"/>
-    <col width="4" customWidth="1" style="19" min="23" max="23"/>
-    <col width="10.83203125" customWidth="1" style="19" min="24" max="25"/>
-    <col width="25.6640625" customWidth="1" style="19" min="26" max="26"/>
-    <col width="2.6640625" customWidth="1" style="19" min="27" max="27"/>
-    <col width="33.1640625" customWidth="1" style="19" min="28" max="28"/>
-    <col width="10.83203125" customWidth="1" style="19" min="29" max="29"/>
-    <col width="25.1640625" customWidth="1" style="19" min="30" max="30"/>
-    <col width="3.5" customWidth="1" style="19" min="31" max="31"/>
-    <col width="9.6640625" customWidth="1" style="19" min="32" max="32"/>
-    <col width="10.83203125" customWidth="1" style="19" min="33" max="33"/>
-    <col width="26.6640625" customWidth="1" style="19" min="34" max="34"/>
-    <col width="4.1640625" customWidth="1" style="19" min="35" max="35"/>
-    <col width="10.83203125" customWidth="1" style="19" min="36" max="37"/>
-    <col width="13.33203125" customWidth="1" style="19" min="38" max="38"/>
-    <col width="10.83203125" customWidth="1" style="19" min="39" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="41" min="1" max="1"/>
+    <col width="24.1640625" customWidth="1" style="41" min="2" max="2"/>
+    <col width="3.1640625" customWidth="1" style="41" min="3" max="3"/>
+    <col width="11.83203125" customWidth="1" style="41" min="4" max="4"/>
+    <col width="10.83203125" customWidth="1" style="41" min="5" max="5"/>
+    <col width="17.1640625" customWidth="1" style="41" min="6" max="6"/>
+    <col width="3.33203125" customWidth="1" style="41" min="7" max="7"/>
+    <col width="11.5" customWidth="1" style="41" min="8" max="8"/>
+    <col width="10.83203125" customWidth="1" style="41" min="9" max="9"/>
+    <col width="15.5" customWidth="1" style="41" min="10" max="10"/>
+    <col width="3.5" customWidth="1" style="41" min="11" max="11"/>
+    <col width="18" customWidth="1" style="41" min="12" max="12"/>
+    <col width="10.83203125" customWidth="1" style="41" min="13" max="13"/>
+    <col width="22.33203125" customWidth="1" style="41" min="14" max="14"/>
+    <col width="5" customWidth="1" style="41" min="15" max="15"/>
+    <col width="16" customWidth="1" style="41" min="16" max="16"/>
+    <col width="10.83203125" customWidth="1" style="41" min="17" max="17"/>
+    <col width="15.83203125" customWidth="1" style="41" min="18" max="18"/>
+    <col width="2.83203125" customWidth="1" style="41" min="19" max="19"/>
+    <col width="10.83203125" customWidth="1" style="41" min="20" max="21"/>
+    <col width="18.83203125" customWidth="1" style="41" min="22" max="22"/>
+    <col width="4" customWidth="1" style="41" min="23" max="23"/>
+    <col width="10.83203125" customWidth="1" style="41" min="24" max="25"/>
+    <col width="25.6640625" customWidth="1" style="41" min="26" max="26"/>
+    <col width="2.6640625" customWidth="1" style="41" min="27" max="27"/>
+    <col width="33.1640625" customWidth="1" style="41" min="28" max="28"/>
+    <col width="10.83203125" customWidth="1" style="41" min="29" max="29"/>
+    <col width="25.1640625" customWidth="1" style="41" min="30" max="30"/>
+    <col width="3.5" customWidth="1" style="41" min="31" max="31"/>
+    <col width="9.6640625" customWidth="1" style="41" min="32" max="32"/>
+    <col width="10.83203125" customWidth="1" style="41" min="33" max="33"/>
+    <col width="26.6640625" customWidth="1" style="41" min="34" max="34"/>
+    <col width="4.1640625" customWidth="1" style="41" min="35" max="35"/>
+    <col width="10.83203125" customWidth="1" style="41" min="36" max="37"/>
+    <col width="13.33203125" customWidth="1" style="41" min="38" max="38"/>
+    <col width="10.83203125" customWidth="1" style="41" min="39" max="39"/>
+    <col width="10.83203125" customWidth="1" style="41" min="40" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
-      <c r="B2" s="49" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>Base + Topper + Ports</t>
         </is>
       </c>
-      <c r="F2" s="49" t="inlineStr">
+      <c r="F2" s="18" t="inlineStr">
         <is>
           <t>Inner</t>
         </is>
       </c>
-      <c r="J2" s="49" t="inlineStr">
+      <c r="J2" s="18" t="inlineStr">
         <is>
           <t>Upper</t>
         </is>
       </c>
-      <c r="N2" s="49" t="inlineStr">
+      <c r="N2" s="18" t="inlineStr">
         <is>
           <t>Camera Focus + Converter</t>
         </is>
       </c>
-      <c r="R2" s="49" t="inlineStr">
+      <c r="R2" s="18" t="inlineStr">
         <is>
           <t>Side-Support</t>
         </is>
       </c>
-      <c r="V2" s="49" t="inlineStr">
+      <c r="V2" s="18" t="inlineStr">
         <is>
           <t>Side-Motor</t>
         </is>
       </c>
-      <c r="Z2" s="49" t="inlineStr">
+      <c r="Z2" s="18" t="inlineStr">
         <is>
           <t>Camera</t>
         </is>
       </c>
-      <c r="AD2" s="49" t="inlineStr">
+      <c r="AD2" s="18" t="inlineStr">
         <is>
           <t>Tripod Mount</t>
         </is>
       </c>
-      <c r="AH2" s="49" t="inlineStr">
+      <c r="AH2" s="18" t="inlineStr">
         <is>
           <t>Comms Mount</t>
         </is>
       </c>
-      <c r="AL2" s="49" t="inlineStr">
+      <c r="AL2" s="18" t="inlineStr">
         <is>
           <t>Hub Display</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="50" t="inlineStr">
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>M2.5 Insert</t>
         </is>
       </c>
-      <c r="C3" s="51" t="n">
-        <v>4</v>
-      </c>
-      <c r="D3" s="52" t="inlineStr">
+      <c r="C3" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t>Sockets</t>
         </is>
       </c>
-      <c r="F3" s="50" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>M3 Insert</t>
         </is>
       </c>
-      <c r="G3" s="51" t="n">
+      <c r="G3" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="H3" s="14" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="H3" s="2" t="n"/>
+      <c r="J3" s="19" t="inlineStr">
         <is>
           <t>M3 Insert</t>
         </is>
       </c>
-      <c r="K3" s="51" t="n">
-        <v>4</v>
-      </c>
-      <c r="L3" s="23" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="K3" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L3" s="9" t="n"/>
+      <c r="N3" s="19" t="inlineStr">
         <is>
           <t>M3 Insert</t>
         </is>
       </c>
-      <c r="O3" s="51" t="n">
-        <v>4</v>
-      </c>
-      <c r="P3" s="23" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="P3" s="9" t="n"/>
+      <c r="R3" s="19" t="inlineStr">
         <is>
           <t>M3 x 30</t>
         </is>
       </c>
-      <c r="S3" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="T3" s="23" t="n"/>
-      <c r="V3" s="50" t="inlineStr">
+      <c r="S3" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" s="9" t="n"/>
+      <c r="V3" s="19" t="inlineStr">
         <is>
           <t>M3 x 16</t>
         </is>
       </c>
-      <c r="W3" s="51" t="n">
-        <v>4</v>
-      </c>
-      <c r="X3" s="52" t="inlineStr">
+      <c r="W3" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="X3" s="21" t="inlineStr">
         <is>
           <t>motor</t>
         </is>
       </c>
-      <c r="Z3" s="50" t="inlineStr">
+      <c r="Z3" s="19" t="inlineStr">
         <is>
           <t>M8 x 25</t>
         </is>
       </c>
-      <c r="AA3" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB3" s="23" t="n"/>
-      <c r="AD3" s="50" t="inlineStr">
+      <c r="AA3" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="9" t="n"/>
+      <c r="AD3" s="19" t="inlineStr">
         <is>
           <t>M5 Nyloc Nut</t>
         </is>
       </c>
-      <c r="AE3" s="51" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF3" s="14" t="n"/>
-      <c r="AH3" s="53" t="inlineStr">
+      <c r="AE3" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF3" s="2" t="n"/>
+      <c r="AH3" s="22" t="inlineStr">
         <is>
           <t>M2 Counter Sunk x 6</t>
         </is>
       </c>
-      <c r="AI3" s="54" t="n">
+      <c r="AI3" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="AJ3" s="32" t="n"/>
-      <c r="AL3" s="50" t="inlineStr">
+      <c r="AJ3" s="12" t="n"/>
+      <c r="AL3" s="19" t="inlineStr">
         <is>
           <t>M3 Insert</t>
         </is>
       </c>
-      <c r="AM3" s="51" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN3" s="23" t="n"/>
+      <c r="AM3" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN3" s="9" t="n"/>
     </row>
     <row r="4">
-      <c r="B4" s="55" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>M3 Insert</t>
         </is>
       </c>
-      <c r="C4" s="56" t="n">
+      <c r="C4" s="40" t="n">
         <v>16</v>
       </c>
-      <c r="D4" s="26" t="n"/>
-      <c r="F4" s="20" t="n"/>
-      <c r="H4" s="21" t="n"/>
-      <c r="J4" s="20" t="n"/>
-      <c r="L4" s="21" t="n"/>
-      <c r="N4" s="55" t="inlineStr">
+      <c r="D4" s="10" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="H4" s="7" t="n"/>
+      <c r="J4" s="6" t="n"/>
+      <c r="L4" s="7" t="n"/>
+      <c r="N4" s="24" t="inlineStr">
         <is>
           <t>M5 Nyloc Nut</t>
         </is>
       </c>
-      <c r="O4" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="P4" s="21" t="n"/>
-      <c r="R4" s="55" t="inlineStr">
+      <c r="O4" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="P4" s="7" t="n"/>
+      <c r="R4" s="24" t="inlineStr">
         <is>
           <t>M3 x 45</t>
         </is>
       </c>
-      <c r="S4" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" s="21" t="n"/>
-      <c r="V4" s="55" t="inlineStr">
+      <c r="S4" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="7" t="n"/>
+      <c r="V4" s="24" t="inlineStr">
         <is>
           <t>M3 x 30</t>
         </is>
       </c>
-      <c r="W4" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="X4" s="21" t="n"/>
-      <c r="Z4" s="55" t="inlineStr">
+      <c r="W4" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="X4" s="7" t="n"/>
+      <c r="Z4" s="24" t="inlineStr">
         <is>
           <t>M8 x 45</t>
         </is>
       </c>
-      <c r="AA4" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="57" t="inlineStr">
+      <c r="AA4" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="26" t="inlineStr">
         <is>
           <t>Pulley</t>
         </is>
       </c>
-      <c r="AD4" s="55" t="inlineStr">
+      <c r="AD4" s="38" t="inlineStr">
         <is>
           <t>3/8 UNC Insert</t>
         </is>
       </c>
-      <c r="AE4" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF4" s="26" t="n"/>
-      <c r="AL4" s="20" t="n"/>
-      <c r="AN4" s="21" t="n"/>
+      <c r="AE4" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AL4" s="6" t="n"/>
+      <c r="AN4" s="7" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="55" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>M5 P Nyloc Nut</t>
         </is>
       </c>
-      <c r="C5" s="56" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" s="26" t="n"/>
-      <c r="F5" s="58" t="inlineStr">
+      <c r="C5" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="10" t="n"/>
+      <c r="F5" s="27" t="inlineStr">
         <is>
           <t>M3 x 8</t>
         </is>
       </c>
-      <c r="G5" s="59" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" s="28" t="n"/>
-      <c r="J5" s="55" t="inlineStr">
+      <c r="G5" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" s="11" t="n"/>
+      <c r="J5" s="24" t="inlineStr">
         <is>
           <t>M3 x 10</t>
         </is>
       </c>
-      <c r="K5" s="56" t="n">
-        <v>4</v>
-      </c>
-      <c r="L5" s="57" t="inlineStr">
+      <c r="K5" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="L5" s="26" t="inlineStr">
         <is>
           <t>motor</t>
         </is>
       </c>
-      <c r="N5" s="20" t="n"/>
-      <c r="P5" s="21" t="n"/>
-      <c r="R5" s="20" t="n"/>
-      <c r="T5" s="21" t="n"/>
-      <c r="V5" s="55" t="inlineStr">
+      <c r="N5" s="6" t="n"/>
+      <c r="P5" s="7" t="n"/>
+      <c r="R5" s="6" t="n"/>
+      <c r="T5" s="7" t="n"/>
+      <c r="V5" s="24" t="inlineStr">
         <is>
           <t>M3 x 45</t>
         </is>
       </c>
-      <c r="W5" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="X5" s="21" t="n"/>
-      <c r="Z5" s="20" t="n"/>
-      <c r="AB5" s="21" t="n"/>
-      <c r="AD5" s="20" t="n"/>
-      <c r="AF5" s="21" t="n"/>
-      <c r="AL5" s="55" t="inlineStr">
+      <c r="W5" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" s="7" t="n"/>
+      <c r="Z5" s="6" t="n"/>
+      <c r="AB5" s="7" t="n"/>
+      <c r="AD5" s="6" t="n"/>
+      <c r="AF5" s="7" t="n"/>
+      <c r="AL5" s="24" t="inlineStr">
         <is>
           <t>M3 x 8</t>
         </is>
       </c>
-      <c r="AM5" s="56" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN5" s="21" t="n"/>
+      <c r="AM5" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN5" s="7" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="20" t="n"/>
-      <c r="D6" s="21" t="n"/>
-      <c r="J6" s="55" t="inlineStr">
+      <c r="B6" s="6" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="J6" s="24" t="inlineStr">
         <is>
           <t>M3 x 30</t>
         </is>
       </c>
-      <c r="K6" s="56" t="n">
+      <c r="K6" s="40" t="n">
         <v>6</v>
       </c>
-      <c r="L6" s="21" t="n"/>
-      <c r="N6" s="55" t="inlineStr">
+      <c r="L6" s="7" t="n"/>
+      <c r="N6" s="24" t="inlineStr">
         <is>
           <t>M3 Counter Sunk x 10</t>
         </is>
       </c>
-      <c r="O6" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="P6" s="21" t="n"/>
-      <c r="R6" s="55" t="inlineStr">
+      <c r="O6" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" s="7" t="n"/>
+      <c r="R6" s="24" t="inlineStr">
         <is>
           <t>M3 Washer</t>
         </is>
       </c>
-      <c r="S6" s="56" t="n">
+      <c r="S6" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="T6" s="21" t="n"/>
-      <c r="V6" s="20" t="n"/>
-      <c r="X6" s="21" t="n"/>
-      <c r="Z6" s="55" t="inlineStr">
+      <c r="T6" s="7" t="n"/>
+      <c r="V6" s="6" t="n"/>
+      <c r="X6" s="7" t="n"/>
+      <c r="Z6" s="24" t="inlineStr">
         <is>
           <t>M8 Domed Nut</t>
         </is>
       </c>
-      <c r="AA6" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB6" s="21" t="n"/>
-      <c r="AD6" s="55" t="inlineStr">
+      <c r="AA6" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB6" s="7" t="n"/>
+      <c r="AD6" s="24" t="inlineStr">
         <is>
           <t>M5 x 20</t>
         </is>
       </c>
-      <c r="AE6" s="56" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF6" s="26" t="n"/>
-      <c r="AL6" s="20" t="n"/>
-      <c r="AN6" s="21" t="n"/>
+      <c r="AE6" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF6" s="10" t="n"/>
+      <c r="AL6" s="6" t="n"/>
+      <c r="AN6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="55" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>M2.5 x 8 CS</t>
         </is>
       </c>
-      <c r="C7" s="56" t="n">
-        <v>4</v>
-      </c>
-      <c r="D7" s="57" t="inlineStr">
+      <c r="C7" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>Sockets</t>
         </is>
       </c>
-      <c r="J7" s="20" t="n"/>
-      <c r="L7" s="21" t="n"/>
-      <c r="N7" s="55" t="inlineStr">
+      <c r="J7" s="6" t="n"/>
+      <c r="L7" s="7" t="n"/>
+      <c r="N7" s="24" t="inlineStr">
         <is>
           <t>M3 x 16</t>
         </is>
       </c>
-      <c r="O7" s="56" t="n">
-        <v>4</v>
-      </c>
-      <c r="P7" s="21" t="n"/>
-      <c r="R7" s="20" t="n"/>
-      <c r="T7" s="21" t="n"/>
-      <c r="V7" s="55" t="inlineStr">
+      <c r="O7" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="P7" s="7" t="n"/>
+      <c r="R7" s="6" t="n"/>
+      <c r="T7" s="7" t="n"/>
+      <c r="V7" s="24" t="inlineStr">
         <is>
           <t>M3 Washer</t>
         </is>
       </c>
-      <c r="W7" s="56" t="n">
+      <c r="W7" s="40" t="n">
         <v>7</v>
       </c>
-      <c r="X7" s="21" t="n"/>
-      <c r="Z7" s="58" t="inlineStr">
+      <c r="X7" s="7" t="n"/>
+      <c r="Z7" s="27" t="inlineStr">
         <is>
           <t>1/4” Camera Thumb Screw</t>
         </is>
       </c>
-      <c r="AA7" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB7" s="22" t="n"/>
-      <c r="AD7" s="58" t="inlineStr">
+      <c r="AA7" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="8" t="n"/>
+      <c r="AD7" s="27" t="inlineStr">
         <is>
           <t>M5 x 30</t>
         </is>
       </c>
-      <c r="AE7" s="59" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF7" s="28" t="n"/>
-      <c r="AL7" s="58" t="inlineStr">
+      <c r="AE7" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF7" s="11" t="n"/>
+      <c r="AL7" s="27" t="inlineStr">
         <is>
           <t>M3 Washer</t>
         </is>
       </c>
-      <c r="AM7" s="59" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN7" s="22" t="n"/>
+      <c r="AM7" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="20" t="n"/>
-      <c r="D8" s="21" t="n"/>
-      <c r="J8" s="58" t="inlineStr">
+      <c r="B8" s="6" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="J8" s="27" t="inlineStr">
         <is>
           <t>M3 Washer</t>
         </is>
       </c>
-      <c r="K8" s="59" t="n">
+      <c r="K8" s="28" t="n">
         <v>10</v>
       </c>
-      <c r="L8" s="22" t="n"/>
-      <c r="N8" s="55" t="inlineStr">
+      <c r="L8" s="8" t="n"/>
+      <c r="N8" s="24" t="inlineStr">
         <is>
           <t>M5 x 25</t>
         </is>
       </c>
-      <c r="O8" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="P8" s="21" t="n"/>
-      <c r="R8" s="58" t="inlineStr">
+      <c r="O8" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="P8" s="7" t="n"/>
+      <c r="R8" s="27" t="inlineStr">
         <is>
           <t>Bearings</t>
         </is>
       </c>
-      <c r="S8" s="59" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" s="22" t="n"/>
-      <c r="V8" s="20" t="n"/>
-      <c r="X8" s="21" t="n"/>
+      <c r="S8" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" s="8" t="n"/>
+      <c r="V8" s="6" t="n"/>
+      <c r="X8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="55" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>M3 Counter Sunk x 10</t>
         </is>
       </c>
-      <c r="C9" s="56" t="n">
-        <v>4</v>
-      </c>
-      <c r="D9" s="57" t="inlineStr">
+      <c r="C9" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="26" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="N9" s="58" t="inlineStr">
+      <c r="N9" s="27" t="inlineStr">
         <is>
           <t>M3 Washer</t>
         </is>
       </c>
-      <c r="O9" s="59" t="n">
-        <v>4</v>
-      </c>
-      <c r="P9" s="22" t="n"/>
-      <c r="V9" s="58" t="inlineStr">
+      <c r="O9" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" s="8" t="n"/>
+      <c r="V9" s="27" t="inlineStr">
         <is>
           <t>Bearings</t>
         </is>
       </c>
-      <c r="W9" s="59" t="n">
-        <v>2</v>
-      </c>
-      <c r="X9" s="22" t="n"/>
+      <c r="W9" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="X9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="20" t="n"/>
-      <c r="D10" s="21" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="D10" s="7" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="55" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>M3 x 12</t>
         </is>
       </c>
-      <c r="C11" s="56" t="n">
+      <c r="C11" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="D11" s="57" t="inlineStr">
+      <c r="D11" s="26" t="inlineStr">
         <is>
           <t>4 Optional</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="55" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>M3 x 20</t>
         </is>
       </c>
-      <c r="C12" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" s="26" t="n"/>
+      <c r="C12" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="55" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>M3 x 45</t>
         </is>
       </c>
-      <c r="C13" s="56" t="n">
+      <c r="C13" s="40" t="n">
         <v>6</v>
       </c>
-      <c r="D13" s="26" t="n"/>
+      <c r="D13" s="10" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="20" t="n"/>
-      <c r="D14" s="21" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="D14" s="7" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="58" t="inlineStr">
+      <c r="B15" s="27" t="inlineStr">
         <is>
           <t>M3 Washer</t>
         </is>
       </c>
-      <c r="C15" s="59" t="n">
+      <c r="C15" s="28" t="n">
         <v>8</v>
       </c>
-      <c r="D15" s="60" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>4 Optional</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18">
-      <c r="F18" s="49" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>Rail End-Comms</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
         <is>
           <t>Rail End</t>
         </is>
       </c>
-      <c r="J18" s="49" t="inlineStr">
+      <c r="J20" s="18" t="inlineStr">
         <is>
           <t>Rail Bottom</t>
         </is>
       </c>
-      <c r="N18" s="49" t="inlineStr">
+      <c r="N20" s="18" t="inlineStr">
         <is>
           <t>Rail Top</t>
         </is>
       </c>
-      <c r="R18" s="49" t="inlineStr">
+      <c r="R20" s="18" t="inlineStr">
         <is>
           <t>Rail Side Drag</t>
         </is>
       </c>
-      <c r="V18" s="49" t="inlineStr">
+      <c r="V20" s="18" t="inlineStr">
         <is>
           <t>Rail Side Motor</t>
         </is>
       </c>
-      <c r="Z18" s="49" t="inlineStr">
+      <c r="Z20" s="18" t="inlineStr">
         <is>
           <t>Rail Drag Arm</t>
         </is>
       </c>
-      <c r="AD18" s="49" t="inlineStr">
+      <c r="AD20" s="18" t="inlineStr">
         <is>
           <t>Rail Drag Clip</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="F19" s="50" t="inlineStr">
+      <c r="AH20" s="37" t="inlineStr">
+        <is>
+          <t>Slider Tripod Mount</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>M3 Nyloc Nut</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="D21" s="2" t="n"/>
+      <c r="F21" s="19" t="inlineStr">
         <is>
           <t>3/8 UNC Insert</t>
         </is>
       </c>
-      <c r="G19" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="14" t="n"/>
-      <c r="J19" s="50" t="inlineStr">
+      <c r="G21" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="2" t="n"/>
+      <c r="J21" s="19" t="inlineStr">
         <is>
           <t>M5 Nyloc Nut</t>
         </is>
       </c>
-      <c r="K19" s="51" t="n">
+      <c r="K21" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="L19" s="23" t="n"/>
-      <c r="N19" s="50" t="inlineStr">
+      <c r="L21" s="9" t="n"/>
+      <c r="N21" s="19" t="inlineStr">
         <is>
           <t>M5 Nyloc Nut</t>
         </is>
       </c>
-      <c r="O19" s="51" t="n">
+      <c r="O21" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="P19" s="23" t="n"/>
-      <c r="R19" s="50" t="inlineStr">
+      <c r="P21" s="9" t="n"/>
+      <c r="R21" s="19" t="inlineStr">
         <is>
           <t>M5 Nyloc Nut</t>
         </is>
       </c>
-      <c r="S19" s="51" t="n">
+      <c r="S21" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="T19" s="23" t="n"/>
-      <c r="V19" s="50" t="inlineStr">
+      <c r="T21" s="9" t="n"/>
+      <c r="V21" s="19" t="inlineStr">
         <is>
           <t>M5 Nyloc Nut</t>
         </is>
       </c>
-      <c r="W19" s="51" t="n">
-        <v>4</v>
-      </c>
-      <c r="X19" s="23" t="n"/>
-      <c r="Z19" s="50" t="inlineStr">
+      <c r="W21" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="X21" s="9" t="n"/>
+      <c r="Z21" s="19" t="inlineStr">
         <is>
           <t>M3 Nyloc Nut</t>
         </is>
       </c>
-      <c r="AA19" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB19" s="23" t="n"/>
-      <c r="AD19" s="50" t="inlineStr">
+      <c r="AA21" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB21" s="9" t="n"/>
+      <c r="AD21" s="19" t="inlineStr">
         <is>
           <t>M3 Nyloc Nut</t>
         </is>
       </c>
-      <c r="AE19" s="51" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF19" s="14" t="n"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="49" t="inlineStr">
-        <is>
-          <t>Rail End-Comms</t>
-        </is>
-      </c>
-      <c r="F20" s="20" t="n"/>
-      <c r="H20" s="21" t="n"/>
-      <c r="J20" s="20" t="n"/>
-      <c r="L20" s="21" t="n"/>
-      <c r="N20" s="20" t="n"/>
-      <c r="P20" s="21" t="n"/>
-      <c r="R20" s="20" t="n"/>
-      <c r="T20" s="21" t="n"/>
-      <c r="V20" s="20" t="n"/>
-      <c r="X20" s="21" t="n"/>
-      <c r="Z20" s="20" t="n"/>
-      <c r="AB20" s="21" t="n"/>
-      <c r="AD20" s="20" t="n"/>
-      <c r="AF20" s="21" t="n"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="50" t="inlineStr">
-        <is>
-          <t>M3 Nyloc Nut</t>
-        </is>
-      </c>
-      <c r="C21" s="51" t="n">
-        <v>7</v>
-      </c>
-      <c r="D21" s="14" t="n"/>
-      <c r="F21" s="55" t="inlineStr">
+      <c r="AE21" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF21" s="2" t="n"/>
+      <c r="AH21" s="39" t="inlineStr">
+        <is>
+          <t>3/8 UNC Insert</t>
+        </is>
+      </c>
+      <c r="AI21" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>M3 Insert</t>
+        </is>
+      </c>
+      <c r="C22" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" s="10" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="H22" s="7" t="n"/>
+      <c r="J22" s="6" t="n"/>
+      <c r="L22" s="7" t="n"/>
+      <c r="N22" s="6" t="n"/>
+      <c r="P22" s="7" t="n"/>
+      <c r="R22" s="6" t="n"/>
+      <c r="T22" s="7" t="n"/>
+      <c r="V22" s="6" t="n"/>
+      <c r="X22" s="7" t="n"/>
+      <c r="Z22" s="6" t="n"/>
+      <c r="AB22" s="7" t="n"/>
+      <c r="AD22" s="6" t="n"/>
+      <c r="AF22" s="7" t="n"/>
+      <c r="AH22" s="6" t="n"/>
+      <c r="AJ22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>3/8 UNC Insert</t>
+        </is>
+      </c>
+      <c r="C23" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="10" t="n"/>
+      <c r="F23" s="24" t="inlineStr">
         <is>
           <t>M5 x 25</t>
         </is>
       </c>
-      <c r="G21" s="56" t="n">
-        <v>4</v>
-      </c>
-      <c r="H21" s="26" t="n"/>
-      <c r="J21" s="55" t="inlineStr">
+      <c r="G23" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" s="10" t="n"/>
+      <c r="J23" s="24" t="inlineStr">
         <is>
           <t>M5 x 35</t>
         </is>
       </c>
-      <c r="K21" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" s="57" t="inlineStr">
+      <c r="K23" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="L23" s="26" t="inlineStr">
         <is>
           <t>(drag-side)</t>
         </is>
       </c>
-      <c r="N21" s="55" t="inlineStr">
+      <c r="N23" s="24" t="inlineStr">
         <is>
           <t>M5 x 35</t>
         </is>
       </c>
-      <c r="O21" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="P21" s="57" t="inlineStr">
+      <c r="O23" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="P23" s="26" t="inlineStr">
         <is>
           <t>(drag-wheels)</t>
         </is>
       </c>
-      <c r="R21" s="58" t="inlineStr">
+      <c r="R23" s="27" t="inlineStr">
         <is>
           <t>M5 x 20</t>
         </is>
       </c>
-      <c r="S21" s="59" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" s="22" t="n"/>
-      <c r="V21" s="55" t="inlineStr">
+      <c r="S23" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" s="8" t="n"/>
+      <c r="V23" s="24" t="inlineStr">
         <is>
           <t>M3 x 10</t>
         </is>
       </c>
-      <c r="W21" s="56" t="n">
-        <v>4</v>
-      </c>
-      <c r="X21" s="21" t="n"/>
-      <c r="Z21" s="58" t="inlineStr">
+      <c r="W23" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="X23" s="7" t="n"/>
+      <c r="Z23" s="27" t="inlineStr">
         <is>
           <t>M5 x 20</t>
         </is>
       </c>
-      <c r="AA21" s="59" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB21" s="22" t="n"/>
-      <c r="AD21" s="55" t="inlineStr">
+      <c r="AA23" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB23" s="8" t="n"/>
+      <c r="AD23" s="24" t="inlineStr">
         <is>
           <t>M3 Counter Sunk x 10</t>
         </is>
       </c>
-      <c r="AE21" s="56" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF21" s="26" t="n"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="55" t="inlineStr">
-        <is>
-          <t>M3 Insert</t>
-        </is>
-      </c>
-      <c r="C22" s="56" t="n">
-        <v>4</v>
-      </c>
-      <c r="D22" s="26" t="n"/>
-      <c r="F22" s="55" t="inlineStr">
+      <c r="AE23" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF23" s="10" t="n"/>
+      <c r="AH23" s="43" t="inlineStr">
+        <is>
+          <t>3/4 UNC 40mm</t>
+        </is>
+      </c>
+      <c r="AI23" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ23" s="11" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="6" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="F24" s="24" t="inlineStr">
         <is>
           <t>M5 x 35</t>
         </is>
       </c>
-      <c r="G22" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="H22" s="26" t="n"/>
-      <c r="J22" s="55" t="inlineStr">
+      <c r="G24" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" s="10" t="n"/>
+      <c r="J24" s="24" t="inlineStr">
         <is>
           <t>M5 x 45</t>
         </is>
       </c>
-      <c r="K22" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" s="57" t="inlineStr">
+      <c r="K24" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="L24" s="26" t="inlineStr">
         <is>
           <t>(motor-wheels)</t>
         </is>
       </c>
-      <c r="N22" s="55" t="inlineStr">
+      <c r="N24" s="24" t="inlineStr">
         <is>
           <t>M5 x 45</t>
         </is>
       </c>
-      <c r="O22" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="P22" s="57" t="inlineStr">
+      <c r="O24" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="P24" s="26" t="inlineStr">
         <is>
           <t>(motor-wheels)</t>
         </is>
       </c>
-      <c r="V22" s="58" t="inlineStr">
+      <c r="V24" s="27" t="inlineStr">
         <is>
           <t>M3 Washer</t>
         </is>
       </c>
-      <c r="W22" s="59" t="n">
-        <v>4</v>
-      </c>
-      <c r="X22" s="22" t="n"/>
-      <c r="AD22" s="20" t="n"/>
-      <c r="AF22" s="21" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="55" t="inlineStr">
-        <is>
-          <t>3/8 UNC Insert</t>
-        </is>
-      </c>
-      <c r="C23" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="26" t="n"/>
-      <c r="F23" s="20" t="n"/>
-      <c r="H23" s="21" t="n"/>
-      <c r="J23" s="55" t="inlineStr">
+      <c r="W24" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="X24" s="8" t="n"/>
+      <c r="AD24" s="6" t="n"/>
+      <c r="AF24" s="7" t="n"/>
+      <c r="AH24" s="41" t="n"/>
+      <c r="AI24" s="41" t="n"/>
+      <c r="AJ24" s="41" t="n"/>
+      <c r="AK24" s="41" t="n"/>
+      <c r="AL24" s="41" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>M3 x 16</t>
+        </is>
+      </c>
+      <c r="C25" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="10" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="H25" s="7" t="n"/>
+      <c r="J25" s="24" t="inlineStr">
         <is>
           <t>M5 x 55</t>
         </is>
       </c>
-      <c r="K23" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="L23" s="57" t="inlineStr">
+      <c r="K25" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" s="26" t="inlineStr">
         <is>
           <t>(bottom-wheels)</t>
         </is>
       </c>
-      <c r="N23" s="58" t="inlineStr">
+      <c r="N25" s="27" t="inlineStr">
         <is>
           <t>M5 x 55</t>
         </is>
       </c>
-      <c r="O23" s="59" t="n">
-        <v>2</v>
-      </c>
-      <c r="P23" s="60" t="inlineStr">
+      <c r="O25" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="P25" s="29" t="inlineStr">
         <is>
           <t>(top-wheels)</t>
         </is>
       </c>
-      <c r="AD23" s="55" t="inlineStr">
+      <c r="AD25" s="24" t="inlineStr">
         <is>
           <t>M3 x 20</t>
         </is>
       </c>
-      <c r="AE23" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF23" s="26" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="20" t="n"/>
-      <c r="D24" s="21" t="n"/>
-      <c r="F24" s="58" t="inlineStr">
+      <c r="AE25" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF25" s="10" t="n"/>
+      <c r="AH25" s="40" t="n"/>
+      <c r="AI25" s="40" t="n"/>
+      <c r="AJ25" s="42" t="n"/>
+      <c r="AK25" s="41" t="n"/>
+      <c r="AL25" s="41" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>M3 x 25</t>
+        </is>
+      </c>
+      <c r="C26" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="10" t="n"/>
+      <c r="F26" s="27" t="inlineStr">
         <is>
           <t>M5 Washer</t>
         </is>
       </c>
-      <c r="G24" s="59" t="n">
-        <v>4</v>
-      </c>
-      <c r="H24" s="28" t="n"/>
-      <c r="J24" s="20" t="n"/>
-      <c r="L24" s="21" t="n"/>
-      <c r="AD24" s="58" t="inlineStr">
+      <c r="G26" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" s="11" t="n"/>
+      <c r="J26" s="6" t="n"/>
+      <c r="L26" s="7" t="n"/>
+      <c r="AD26" s="27" t="inlineStr">
         <is>
           <t>M3 Washer</t>
         </is>
       </c>
-      <c r="AE24" s="59" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF24" s="28" t="n"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="55" t="inlineStr">
-        <is>
-          <t>M3 x 16</t>
-        </is>
-      </c>
-      <c r="C25" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="D25" s="26" t="n"/>
-      <c r="J25" s="55" t="inlineStr">
+      <c r="AE26" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF26" s="11" t="n"/>
+      <c r="AH26" s="40" t="n"/>
+      <c r="AI26" s="40" t="n"/>
+      <c r="AJ26" s="42" t="n"/>
+      <c r="AK26" s="41" t="n"/>
+      <c r="AL26" s="41" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>M3 Counter Sunk x 10</t>
+        </is>
+      </c>
+      <c r="C27" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" s="10" t="n"/>
+      <c r="J27" s="24" t="inlineStr">
         <is>
           <t>M3 x 25</t>
         </is>
       </c>
-      <c r="K25" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" s="57" t="inlineStr">
+      <c r="K27" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="L27" s="26" t="inlineStr">
         <is>
           <t>(optional cover)</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="55" t="inlineStr">
-        <is>
-          <t>M3 x 25</t>
-        </is>
-      </c>
-      <c r="C26" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="26" t="n"/>
-      <c r="J26" s="58" t="inlineStr">
+      <c r="AH27" s="41" t="n"/>
+      <c r="AI27" s="41" t="n"/>
+      <c r="AJ27" s="41" t="n"/>
+      <c r="AK27" s="41" t="n"/>
+      <c r="AL27" s="41" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="6" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="J28" s="27" t="inlineStr">
         <is>
           <t>M3 Washer</t>
         </is>
       </c>
-      <c r="K26" s="59" t="n">
-        <v>2</v>
-      </c>
-      <c r="L26" s="60" t="inlineStr">
+      <c r="K28" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" s="29" t="inlineStr">
         <is>
           <t>(optional cover)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="55" t="inlineStr">
-        <is>
-          <t>M3 Counter Sunk x 10</t>
-        </is>
-      </c>
-      <c r="C27" s="56" t="n">
-        <v>4</v>
-      </c>
-      <c r="D27" s="26" t="n"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="20" t="n"/>
-      <c r="D28" s="21" t="n"/>
-    </row>
     <row r="29">
-      <c r="B29" s="55" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>M5 x 25</t>
         </is>
       </c>
-      <c r="C29" s="56" t="n">
-        <v>4</v>
-      </c>
-      <c r="D29" s="26" t="n"/>
+      <c r="C29" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" s="10" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="20" t="n"/>
-      <c r="D30" s="21" t="n"/>
+      <c r="B30" s="6" t="n"/>
+      <c r="D30" s="7" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="55" t="inlineStr">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>M3 Washer</t>
         </is>
       </c>
-      <c r="C31" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="D31" s="26" t="n"/>
+      <c r="C31" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="10" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="58" t="inlineStr">
+      <c r="B32" s="27" t="inlineStr">
         <is>
           <t>M5 Washer</t>
         </is>
       </c>
-      <c r="C32" s="59" t="n">
-        <v>4</v>
-      </c>
-      <c r="D32" s="28" t="n"/>
-      <c r="G32" s="1" t="n"/>
-      <c r="H32" s="1" t="n"/>
-      <c r="I32" s="1" t="n"/>
-      <c r="J32" s="1" t="n"/>
-      <c r="K32" s="1" t="n"/>
-      <c r="L32" s="1" t="n"/>
+      <c r="C32" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" s="11" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="1" t="n"/>
+      <c r="B33" s="42" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="1" t="n"/>
+      <c r="B34" s="42" t="n"/>
+      <c r="G34" s="42" t="n"/>
+      <c r="H34" s="42" t="n"/>
+      <c r="I34" s="42" t="n"/>
+      <c r="J34" s="42" t="n"/>
+      <c r="K34" s="42" t="n"/>
+      <c r="L34" s="42" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="1" t="n"/>
+      <c r="B35" s="42" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="1" t="n"/>
+      <c r="B36" s="42" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="1" t="n"/>
+      <c r="B37" s="42" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="1" t="n"/>
+      <c r="B38" s="42" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="1" t="n"/>
+      <c r="B39" s="42" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="1" t="n"/>
+      <c r="B40" s="42" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="1" t="n"/>
+      <c r="B41" s="42" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="1" t="n"/>
+      <c r="B42" s="42" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="1" t="n"/>
+      <c r="B43" s="42" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="1" t="n"/>
+      <c r="B44" s="42" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="1" t="n"/>
+      <c r="B45" s="42" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="1" t="n"/>
+      <c r="B46" s="42" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="1" t="n"/>
+      <c r="B47" s="42" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="1" t="n"/>
+      <c r="B48" s="42" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="1" t="n"/>
+      <c r="B49" s="42" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="1" t="n"/>
+      <c r="B50" s="42" t="n"/>
     </row>
     <row r="51">
-      <c r="B51" s="1" t="n"/>
+      <c r="B51" s="42" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="1" t="n"/>
+      <c r="B52" s="42" t="n"/>
     </row>
     <row r="53">
-      <c r="B53" s="1" t="n"/>
+      <c r="B53" s="42" t="n"/>
     </row>
     <row r="54">
-      <c r="B54" s="1" t="n"/>
+      <c r="B54" s="42" t="n"/>
     </row>
     <row r="55">
-      <c r="B55" s="1" t="n"/>
+      <c r="B55" s="42" t="n"/>
     </row>
     <row r="56">
-      <c r="B56" s="1" t="n"/>
+      <c r="B56" s="42" t="n"/>
     </row>
     <row r="57">
-      <c r="B57" s="1" t="n"/>
+      <c r="B57" s="42" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3012,807 +3036,815 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U33"/>
+  <dimension ref="B2:V35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="3.33203125" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="12"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
-    <col width="9" customWidth="1" min="19" max="19"/>
-    <col width="9" customWidth="1" min="20" max="20"/>
-    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="3" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2">
-      <c r="B2" s="61" t="inlineStr">
+    <row r="2" ht="57" customHeight="1">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>Fastener</t>
         </is>
       </c>
-      <c r="C2" s="61" t="inlineStr">
+      <c r="C2" s="30" t="inlineStr">
         <is>
           <t>Base + Topper + Ports</t>
         </is>
       </c>
-      <c r="D2" s="61" t="inlineStr">
+      <c r="D2" s="30" t="inlineStr">
         <is>
           <t>Inner</t>
         </is>
       </c>
-      <c r="E2" s="61" t="inlineStr">
+      <c r="E2" s="30" t="inlineStr">
         <is>
           <t>Upper</t>
         </is>
       </c>
-      <c r="F2" s="61" t="inlineStr">
+      <c r="F2" s="30" t="inlineStr">
         <is>
           <t>Camera Focus + Converter</t>
         </is>
       </c>
-      <c r="G2" s="61" t="inlineStr">
+      <c r="G2" s="30" t="inlineStr">
         <is>
           <t>Side-Support</t>
         </is>
       </c>
-      <c r="H2" s="61" t="inlineStr">
+      <c r="H2" s="30" t="inlineStr">
         <is>
           <t>Side-Motor</t>
         </is>
       </c>
-      <c r="I2" s="61" t="inlineStr">
+      <c r="I2" s="30" t="inlineStr">
         <is>
           <t>Camera</t>
         </is>
       </c>
-      <c r="J2" s="61" t="inlineStr">
+      <c r="J2" s="30" t="inlineStr">
         <is>
           <t>Tripod Mount</t>
         </is>
       </c>
-      <c r="K2" s="61" t="inlineStr">
+      <c r="K2" s="30" t="inlineStr">
         <is>
           <t>Comms Mount</t>
         </is>
       </c>
-      <c r="L2" s="61" t="inlineStr">
+      <c r="L2" s="30" t="inlineStr">
         <is>
           <t>Hub Display</t>
         </is>
       </c>
-      <c r="M2" s="61" t="inlineStr">
+      <c r="M2" s="30" t="inlineStr">
         <is>
           <t>Rail End-Comms</t>
         </is>
       </c>
-      <c r="N2" s="61" t="inlineStr">
+      <c r="N2" s="30" t="inlineStr">
         <is>
           <t>Rail End</t>
         </is>
       </c>
-      <c r="O2" s="61" t="inlineStr">
+      <c r="O2" s="30" t="inlineStr">
         <is>
           <t>Rail Bottom</t>
         </is>
       </c>
-      <c r="P2" s="61" t="inlineStr">
+      <c r="P2" s="30" t="inlineStr">
         <is>
           <t>Rail Top</t>
         </is>
       </c>
-      <c r="Q2" s="61" t="inlineStr">
+      <c r="Q2" s="30" t="inlineStr">
         <is>
           <t>Rail Side Drag</t>
         </is>
       </c>
-      <c r="R2" s="61" t="inlineStr">
+      <c r="R2" s="30" t="inlineStr">
         <is>
           <t>Rail Side Motor</t>
         </is>
       </c>
-      <c r="S2" s="61" t="inlineStr">
+      <c r="S2" s="30" t="inlineStr">
         <is>
           <t>Rail Drag Arm</t>
         </is>
       </c>
-      <c r="T2" s="61" t="inlineStr">
+      <c r="T2" s="30" t="inlineStr">
         <is>
           <t>Rail Drag Clip</t>
         </is>
       </c>
-      <c r="U2" s="61" t="inlineStr">
+      <c r="U2" s="44" t="inlineStr">
+        <is>
+          <t>Slider Tripod Mount</t>
+        </is>
+      </c>
+      <c r="V2" s="30" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="62" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>M3 x 8</t>
         </is>
       </c>
-      <c r="C3" s="47" t="n"/>
-      <c r="D3" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" s="47" t="n"/>
-      <c r="F3" s="47" t="n"/>
-      <c r="G3" s="47" t="n"/>
-      <c r="H3" s="47" t="n"/>
-      <c r="I3" s="47" t="n"/>
-      <c r="J3" s="47" t="n"/>
-      <c r="K3" s="47" t="n"/>
-      <c r="L3" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="M3" s="47" t="n"/>
-      <c r="N3" s="47" t="n"/>
-      <c r="O3" s="47" t="n"/>
-      <c r="P3" s="47" t="n"/>
-      <c r="Q3" s="47" t="n"/>
-      <c r="R3" s="47" t="n"/>
-      <c r="S3" s="47" t="n"/>
-      <c r="T3" s="47" t="n"/>
-      <c r="U3" s="63">
-        <f>SUM(C3:T3)</f>
+      <c r="C3" s="16" t="n"/>
+      <c r="D3" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" s="16" t="n"/>
+      <c r="F3" s="16" t="n"/>
+      <c r="G3" s="16" t="n"/>
+      <c r="H3" s="16" t="n"/>
+      <c r="I3" s="16" t="n"/>
+      <c r="J3" s="16" t="n"/>
+      <c r="K3" s="16" t="n"/>
+      <c r="L3" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="M3" s="16" t="n"/>
+      <c r="N3" s="16" t="n"/>
+      <c r="O3" s="16" t="n"/>
+      <c r="P3" s="16" t="n"/>
+      <c r="Q3" s="16" t="n"/>
+      <c r="R3" s="16" t="n"/>
+      <c r="S3" s="16" t="n"/>
+      <c r="T3" s="16" t="n"/>
+      <c r="U3" s="16" t="n"/>
+      <c r="V3" s="32">
+        <f>SUM(C3:U3)</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="62" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>M3 x 10</t>
         </is>
       </c>
-      <c r="C4" s="47" t="n"/>
-      <c r="D4" s="47" t="n"/>
-      <c r="E4" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" s="47" t="n"/>
-      <c r="G4" s="47" t="n"/>
-      <c r="H4" s="47" t="n"/>
-      <c r="I4" s="47" t="n"/>
-      <c r="J4" s="47" t="n"/>
-      <c r="K4" s="47" t="n"/>
-      <c r="L4" s="47" t="n"/>
-      <c r="M4" s="47" t="n"/>
-      <c r="N4" s="47" t="n"/>
-      <c r="O4" s="47" t="n"/>
-      <c r="P4" s="47" t="n"/>
-      <c r="Q4" s="47" t="n"/>
-      <c r="R4" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="S4" s="47" t="n"/>
-      <c r="T4" s="47" t="n"/>
-      <c r="U4" s="63">
-        <f>SUM(C4:T4)</f>
+      <c r="C4" s="16" t="n"/>
+      <c r="D4" s="16" t="n"/>
+      <c r="E4" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="16" t="n"/>
+      <c r="G4" s="16" t="n"/>
+      <c r="H4" s="16" t="n"/>
+      <c r="I4" s="16" t="n"/>
+      <c r="J4" s="16" t="n"/>
+      <c r="K4" s="16" t="n"/>
+      <c r="L4" s="16" t="n"/>
+      <c r="M4" s="16" t="n"/>
+      <c r="N4" s="16" t="n"/>
+      <c r="O4" s="16" t="n"/>
+      <c r="P4" s="16" t="n"/>
+      <c r="Q4" s="16" t="n"/>
+      <c r="R4" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="S4" s="16" t="n"/>
+      <c r="T4" s="16" t="n"/>
+      <c r="U4" s="16" t="n"/>
+      <c r="V4" s="32">
+        <f>SUM(C4:U4)</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="62" t="inlineStr">
+      <c r="B5" s="31" t="inlineStr">
         <is>
           <t>M3 x 12</t>
         </is>
       </c>
-      <c r="C5" s="47" t="n">
+      <c r="C5" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="D5" s="47" t="n"/>
-      <c r="E5" s="47" t="n"/>
-      <c r="F5" s="47" t="n"/>
-      <c r="G5" s="47" t="n"/>
-      <c r="H5" s="47" t="n"/>
-      <c r="I5" s="47" t="n"/>
-      <c r="J5" s="47" t="n"/>
-      <c r="K5" s="47" t="n"/>
-      <c r="L5" s="47" t="n"/>
-      <c r="M5" s="47" t="n"/>
-      <c r="N5" s="47" t="n"/>
-      <c r="O5" s="47" t="n"/>
-      <c r="P5" s="47" t="n"/>
-      <c r="Q5" s="47" t="n"/>
-      <c r="R5" s="47" t="n"/>
-      <c r="S5" s="47" t="n"/>
-      <c r="T5" s="47" t="n"/>
-      <c r="U5" s="63">
-        <f>SUM(C5:T5)</f>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="16" t="n"/>
+      <c r="G5" s="16" t="n"/>
+      <c r="H5" s="16" t="n"/>
+      <c r="I5" s="16" t="n"/>
+      <c r="J5" s="16" t="n"/>
+      <c r="K5" s="16" t="n"/>
+      <c r="L5" s="16" t="n"/>
+      <c r="M5" s="16" t="n"/>
+      <c r="N5" s="16" t="n"/>
+      <c r="O5" s="16" t="n"/>
+      <c r="P5" s="16" t="n"/>
+      <c r="Q5" s="16" t="n"/>
+      <c r="R5" s="16" t="n"/>
+      <c r="S5" s="16" t="n"/>
+      <c r="T5" s="16" t="n"/>
+      <c r="U5" s="16" t="n"/>
+      <c r="V5" s="32">
+        <f>SUM(C5:U5)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="62" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>M3 x 16</t>
         </is>
       </c>
-      <c r="C6" s="47" t="n"/>
-      <c r="D6" s="47" t="n"/>
-      <c r="E6" s="47" t="n"/>
-      <c r="F6" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="G6" s="47" t="n"/>
-      <c r="H6" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" s="47" t="n"/>
-      <c r="J6" s="47" t="n"/>
-      <c r="K6" s="47" t="n"/>
-      <c r="L6" s="47" t="n"/>
-      <c r="M6" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="N6" s="47" t="n"/>
-      <c r="O6" s="47" t="n"/>
-      <c r="P6" s="47" t="n"/>
-      <c r="Q6" s="47" t="n"/>
-      <c r="R6" s="47" t="n"/>
-      <c r="S6" s="47" t="n"/>
-      <c r="T6" s="47" t="n"/>
-      <c r="U6" s="63">
-        <f>SUM(C6:T6)</f>
+      <c r="C6" s="16" t="n"/>
+      <c r="D6" s="16" t="n"/>
+      <c r="E6" s="16" t="n"/>
+      <c r="F6" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="16" t="n"/>
+      <c r="H6" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" s="16" t="n"/>
+      <c r="J6" s="16" t="n"/>
+      <c r="K6" s="16" t="n"/>
+      <c r="L6" s="16" t="n"/>
+      <c r="M6" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" s="16" t="n"/>
+      <c r="O6" s="16" t="n"/>
+      <c r="P6" s="16" t="n"/>
+      <c r="Q6" s="16" t="n"/>
+      <c r="R6" s="16" t="n"/>
+      <c r="S6" s="16" t="n"/>
+      <c r="T6" s="16" t="n"/>
+      <c r="U6" s="16" t="n"/>
+      <c r="V6" s="32">
+        <f>SUM(C6:U6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="62" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>M3 x 20</t>
         </is>
       </c>
-      <c r="C7" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="47" t="n"/>
-      <c r="E7" s="47" t="n"/>
-      <c r="F7" s="47" t="n"/>
-      <c r="G7" s="47" t="n"/>
-      <c r="H7" s="47" t="n"/>
-      <c r="I7" s="47" t="n"/>
-      <c r="J7" s="47" t="n"/>
-      <c r="K7" s="47" t="n"/>
-      <c r="L7" s="47" t="n"/>
-      <c r="M7" s="47" t="n"/>
-      <c r="N7" s="47" t="n"/>
-      <c r="O7" s="47" t="n"/>
-      <c r="P7" s="47" t="n"/>
-      <c r="Q7" s="47" t="n"/>
-      <c r="R7" s="47" t="n"/>
-      <c r="S7" s="47" t="n"/>
-      <c r="T7" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" s="63">
-        <f>SUM(C7:T7)</f>
+      <c r="C7" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="16" t="n"/>
+      <c r="G7" s="16" t="n"/>
+      <c r="H7" s="16" t="n"/>
+      <c r="I7" s="16" t="n"/>
+      <c r="J7" s="16" t="n"/>
+      <c r="K7" s="16" t="n"/>
+      <c r="L7" s="16" t="n"/>
+      <c r="M7" s="16" t="n"/>
+      <c r="N7" s="16" t="n"/>
+      <c r="O7" s="16" t="n"/>
+      <c r="P7" s="16" t="n"/>
+      <c r="Q7" s="16" t="n"/>
+      <c r="R7" s="16" t="n"/>
+      <c r="S7" s="16" t="n"/>
+      <c r="T7" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" s="16" t="n"/>
+      <c r="V7" s="32">
+        <f>SUM(C7:U7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="62" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>M3 x 25</t>
         </is>
       </c>
-      <c r="C8" s="47" t="n"/>
-      <c r="D8" s="47" t="n"/>
-      <c r="E8" s="47" t="n"/>
-      <c r="F8" s="47" t="n"/>
-      <c r="G8" s="47" t="n"/>
-      <c r="H8" s="47" t="n"/>
-      <c r="I8" s="47" t="n"/>
-      <c r="J8" s="47" t="n"/>
-      <c r="K8" s="47" t="n"/>
-      <c r="L8" s="47" t="n"/>
-      <c r="M8" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" s="47" t="n"/>
-      <c r="O8" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="P8" s="47" t="n"/>
-      <c r="Q8" s="47" t="n"/>
-      <c r="R8" s="47" t="n"/>
-      <c r="S8" s="47" t="n"/>
-      <c r="T8" s="47" t="n"/>
-      <c r="U8" s="63">
-        <f>SUM(C8:T8)</f>
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="16" t="n"/>
+      <c r="E8" s="16" t="n"/>
+      <c r="F8" s="16" t="n"/>
+      <c r="G8" s="16" t="n"/>
+      <c r="H8" s="16" t="n"/>
+      <c r="I8" s="16" t="n"/>
+      <c r="J8" s="16" t="n"/>
+      <c r="K8" s="16" t="n"/>
+      <c r="L8" s="16" t="n"/>
+      <c r="M8" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="16" t="n"/>
+      <c r="O8" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="P8" s="16" t="n"/>
+      <c r="Q8" s="16" t="n"/>
+      <c r="R8" s="16" t="n"/>
+      <c r="S8" s="16" t="n"/>
+      <c r="T8" s="16" t="n"/>
+      <c r="U8" s="16" t="n"/>
+      <c r="V8" s="32">
+        <f>SUM(C8:U8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="62" t="inlineStr">
+      <c r="B9" s="31" t="inlineStr">
         <is>
           <t>M3 x 30</t>
         </is>
       </c>
-      <c r="C9" s="47" t="n"/>
-      <c r="D9" s="47" t="n"/>
-      <c r="E9" s="47" t="n">
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="F9" s="47" t="n"/>
-      <c r="G9" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" s="47" t="n"/>
-      <c r="J9" s="47" t="n"/>
-      <c r="K9" s="47" t="n"/>
-      <c r="L9" s="47" t="n"/>
-      <c r="M9" s="47" t="n"/>
-      <c r="N9" s="47" t="n"/>
-      <c r="O9" s="47" t="n"/>
-      <c r="P9" s="47" t="n"/>
-      <c r="Q9" s="47" t="n"/>
-      <c r="R9" s="47" t="n"/>
-      <c r="S9" s="47" t="n"/>
-      <c r="T9" s="47" t="n"/>
-      <c r="U9" s="63">
-        <f>SUM(C9:T9)</f>
+      <c r="F9" s="16" t="n"/>
+      <c r="G9" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="16" t="n"/>
+      <c r="J9" s="16" t="n"/>
+      <c r="K9" s="16" t="n"/>
+      <c r="L9" s="16" t="n"/>
+      <c r="M9" s="16" t="n"/>
+      <c r="N9" s="16" t="n"/>
+      <c r="O9" s="16" t="n"/>
+      <c r="P9" s="16" t="n"/>
+      <c r="Q9" s="16" t="n"/>
+      <c r="R9" s="16" t="n"/>
+      <c r="S9" s="16" t="n"/>
+      <c r="T9" s="16" t="n"/>
+      <c r="U9" s="16" t="n"/>
+      <c r="V9" s="32">
+        <f>SUM(C9:U9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="62" t="inlineStr">
+      <c r="B10" s="31" t="inlineStr">
         <is>
           <t>M3 x 45</t>
         </is>
       </c>
-      <c r="C10" s="47" t="n">
+      <c r="C10" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="D10" s="47" t="n"/>
-      <c r="E10" s="47" t="n"/>
-      <c r="F10" s="47" t="n"/>
-      <c r="G10" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="47" t="n"/>
-      <c r="J10" s="47" t="n"/>
-      <c r="K10" s="47" t="n"/>
-      <c r="L10" s="47" t="n"/>
-      <c r="M10" s="47" t="n"/>
-      <c r="N10" s="47" t="n"/>
-      <c r="O10" s="47" t="n"/>
-      <c r="P10" s="47" t="n"/>
-      <c r="Q10" s="47" t="n"/>
-      <c r="R10" s="47" t="n"/>
-      <c r="S10" s="47" t="n"/>
-      <c r="T10" s="47" t="n"/>
-      <c r="U10" s="63">
-        <f>SUM(C10:T10)</f>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="16" t="n"/>
+      <c r="G10" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="16" t="n"/>
+      <c r="J10" s="16" t="n"/>
+      <c r="K10" s="16" t="n"/>
+      <c r="L10" s="16" t="n"/>
+      <c r="M10" s="16" t="n"/>
+      <c r="N10" s="16" t="n"/>
+      <c r="O10" s="16" t="n"/>
+      <c r="P10" s="16" t="n"/>
+      <c r="Q10" s="16" t="n"/>
+      <c r="R10" s="16" t="n"/>
+      <c r="S10" s="16" t="n"/>
+      <c r="T10" s="16" t="n"/>
+      <c r="U10" s="16" t="n"/>
+      <c r="V10" s="32">
+        <f>SUM(C10:U10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="16" t="n"/>
-      <c r="G11" s="16" t="n"/>
-      <c r="H11" s="16" t="n"/>
-      <c r="I11" s="16" t="n"/>
-      <c r="J11" s="16" t="n"/>
-      <c r="K11" s="16" t="n"/>
-      <c r="L11" s="16" t="n"/>
-      <c r="M11" s="16" t="n"/>
-      <c r="N11" s="16" t="n"/>
-      <c r="O11" s="16" t="n"/>
-      <c r="P11" s="16" t="n"/>
-      <c r="Q11" s="16" t="n"/>
-      <c r="R11" s="16" t="n"/>
-      <c r="S11" s="16" t="n"/>
-      <c r="T11" s="17" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4" t="n"/>
+      <c r="Q11" s="4" t="n"/>
+      <c r="R11" s="4" t="n"/>
+      <c r="S11" s="4" t="n"/>
+      <c r="T11" s="4" t="n"/>
+      <c r="U11" s="4" t="n"/>
+      <c r="V11" s="4" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="62" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>M2 Counter Sunk x 6</t>
         </is>
       </c>
-      <c r="C12" s="47" t="n"/>
-      <c r="D12" s="47" t="n"/>
-      <c r="E12" s="47" t="n"/>
-      <c r="F12" s="47" t="n"/>
-      <c r="G12" s="47" t="n"/>
-      <c r="H12" s="47" t="n"/>
-      <c r="I12" s="47" t="n"/>
-      <c r="J12" s="47" t="n"/>
-      <c r="K12" s="47" t="n">
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
+      <c r="G12" s="16" t="n"/>
+      <c r="H12" s="16" t="n"/>
+      <c r="I12" s="16" t="n"/>
+      <c r="J12" s="16" t="n"/>
+      <c r="K12" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="L12" s="47" t="n"/>
-      <c r="M12" s="47" t="n"/>
-      <c r="N12" s="47" t="n"/>
-      <c r="O12" s="47" t="n"/>
-      <c r="P12" s="47" t="n"/>
-      <c r="Q12" s="47" t="n"/>
-      <c r="R12" s="47" t="n"/>
-      <c r="S12" s="47" t="n"/>
-      <c r="T12" s="47" t="n"/>
-      <c r="U12" s="63">
-        <f>SUM(C12:T12)</f>
+      <c r="L12" s="16" t="n"/>
+      <c r="M12" s="16" t="n"/>
+      <c r="N12" s="16" t="n"/>
+      <c r="O12" s="16" t="n"/>
+      <c r="P12" s="16" t="n"/>
+      <c r="Q12" s="16" t="n"/>
+      <c r="R12" s="16" t="n"/>
+      <c r="S12" s="16" t="n"/>
+      <c r="T12" s="16" t="n"/>
+      <c r="U12" s="16" t="n"/>
+      <c r="V12" s="32">
+        <f>SUM(C12:U12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="62" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>M3 Counter Sunk x 10</t>
         </is>
       </c>
-      <c r="C13" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" s="47" t="n"/>
-      <c r="E13" s="47" t="n"/>
-      <c r="F13" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" s="47" t="n"/>
-      <c r="H13" s="47" t="n"/>
-      <c r="I13" s="47" t="n"/>
-      <c r="J13" s="47" t="n"/>
-      <c r="K13" s="47" t="n"/>
-      <c r="L13" s="47" t="n"/>
-      <c r="M13" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="N13" s="47" t="n"/>
-      <c r="O13" s="47" t="n"/>
-      <c r="P13" s="47" t="n"/>
-      <c r="Q13" s="47" t="n"/>
-      <c r="R13" s="47" t="n"/>
-      <c r="S13" s="47" t="n"/>
-      <c r="T13" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="U13" s="63">
-        <f>SUM(C13:T13)</f>
+      <c r="C13" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="16" t="n"/>
+      <c r="E13" s="16" t="n"/>
+      <c r="F13" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="16" t="n"/>
+      <c r="H13" s="16" t="n"/>
+      <c r="I13" s="16" t="n"/>
+      <c r="J13" s="16" t="n"/>
+      <c r="K13" s="16" t="n"/>
+      <c r="L13" s="16" t="n"/>
+      <c r="M13" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="N13" s="16" t="n"/>
+      <c r="O13" s="16" t="n"/>
+      <c r="P13" s="16" t="n"/>
+      <c r="Q13" s="16" t="n"/>
+      <c r="R13" s="16" t="n"/>
+      <c r="S13" s="16" t="n"/>
+      <c r="T13" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" s="16" t="n"/>
+      <c r="V13" s="32">
+        <f>SUM(C13:U13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="15" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
-      <c r="G14" s="16" t="n"/>
-      <c r="H14" s="16" t="n"/>
-      <c r="I14" s="16" t="n"/>
-      <c r="J14" s="16" t="n"/>
-      <c r="K14" s="16" t="n"/>
-      <c r="L14" s="16" t="n"/>
-      <c r="M14" s="16" t="n"/>
-      <c r="N14" s="16" t="n"/>
-      <c r="O14" s="16" t="n"/>
-      <c r="P14" s="16" t="n"/>
-      <c r="Q14" s="16" t="n"/>
-      <c r="R14" s="16" t="n"/>
-      <c r="S14" s="16" t="n"/>
-      <c r="T14" s="17" t="n"/>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
+      <c r="P14" s="4" t="n"/>
+      <c r="Q14" s="4" t="n"/>
+      <c r="R14" s="4" t="n"/>
+      <c r="S14" s="4" t="n"/>
+      <c r="T14" s="4" t="n"/>
+      <c r="U14" s="4" t="n"/>
+      <c r="V14" s="4" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="62" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>M5 x 20</t>
         </is>
       </c>
-      <c r="C15" s="47" t="n"/>
-      <c r="D15" s="47" t="n"/>
-      <c r="E15" s="47" t="n"/>
-      <c r="F15" s="47" t="n"/>
-      <c r="G15" s="47" t="n"/>
-      <c r="H15" s="47" t="n"/>
-      <c r="I15" s="47" t="n"/>
-      <c r="J15" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="K15" s="47" t="n"/>
-      <c r="L15" s="47" t="n"/>
-      <c r="M15" s="47" t="n"/>
-      <c r="N15" s="47" t="n"/>
-      <c r="O15" s="47" t="n"/>
-      <c r="P15" s="47" t="n"/>
-      <c r="Q15" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" s="47" t="n"/>
-      <c r="S15" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" s="47" t="n"/>
-      <c r="U15" s="63">
-        <f>SUM(C15:T15)</f>
+      <c r="C15" s="16" t="n"/>
+      <c r="D15" s="16" t="n"/>
+      <c r="E15" s="16" t="n"/>
+      <c r="F15" s="16" t="n"/>
+      <c r="G15" s="16" t="n"/>
+      <c r="H15" s="16" t="n"/>
+      <c r="I15" s="16" t="n"/>
+      <c r="J15" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" s="16" t="n"/>
+      <c r="L15" s="16" t="n"/>
+      <c r="M15" s="16" t="n"/>
+      <c r="N15" s="16" t="n"/>
+      <c r="O15" s="16" t="n"/>
+      <c r="P15" s="16" t="n"/>
+      <c r="Q15" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" s="16" t="n"/>
+      <c r="S15" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" s="16" t="n"/>
+      <c r="U15" s="16" t="n"/>
+      <c r="V15" s="32">
+        <f>SUM(C15:U15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="62" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>M5 x 25</t>
         </is>
       </c>
-      <c r="C16" s="47" t="n"/>
-      <c r="D16" s="47" t="n"/>
-      <c r="E16" s="47" t="n"/>
-      <c r="F16" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" s="47" t="n"/>
-      <c r="H16" s="47" t="n"/>
-      <c r="I16" s="47" t="n"/>
-      <c r="J16" s="47" t="n"/>
-      <c r="K16" s="47" t="n"/>
-      <c r="L16" s="47" t="n"/>
-      <c r="M16" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="N16" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="O16" s="47" t="n"/>
-      <c r="P16" s="47" t="n"/>
-      <c r="Q16" s="47" t="n"/>
-      <c r="R16" s="47" t="n"/>
-      <c r="S16" s="47" t="n"/>
-      <c r="T16" s="47" t="n"/>
-      <c r="U16" s="63">
-        <f>SUM(C16:T16)</f>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="16" t="n"/>
+      <c r="H16" s="16" t="n"/>
+      <c r="I16" s="16" t="n"/>
+      <c r="J16" s="16" t="n"/>
+      <c r="K16" s="16" t="n"/>
+      <c r="L16" s="16" t="n"/>
+      <c r="M16" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="N16" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O16" s="16" t="n"/>
+      <c r="P16" s="16" t="n"/>
+      <c r="Q16" s="16" t="n"/>
+      <c r="R16" s="16" t="n"/>
+      <c r="S16" s="16" t="n"/>
+      <c r="T16" s="16" t="n"/>
+      <c r="U16" s="16" t="n"/>
+      <c r="V16" s="32">
+        <f>SUM(C16:U16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="62" t="inlineStr">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>M5 x 30</t>
         </is>
       </c>
-      <c r="C17" s="47" t="n"/>
-      <c r="D17" s="47" t="n"/>
-      <c r="E17" s="47" t="n"/>
-      <c r="F17" s="47" t="n"/>
-      <c r="G17" s="47" t="n"/>
-      <c r="H17" s="47" t="n"/>
-      <c r="I17" s="47" t="n"/>
-      <c r="J17" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" s="47" t="n"/>
-      <c r="L17" s="47" t="n"/>
-      <c r="M17" s="47" t="n"/>
-      <c r="N17" s="47" t="n"/>
-      <c r="O17" s="47" t="n"/>
-      <c r="P17" s="47" t="n"/>
-      <c r="Q17" s="47" t="n"/>
-      <c r="R17" s="47" t="n"/>
-      <c r="S17" s="47" t="n"/>
-      <c r="T17" s="47" t="n"/>
-      <c r="U17" s="63">
-        <f>SUM(C17:T17)</f>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="16" t="n"/>
+      <c r="G17" s="16" t="n"/>
+      <c r="H17" s="16" t="n"/>
+      <c r="I17" s="16" t="n"/>
+      <c r="J17" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" s="16" t="n"/>
+      <c r="L17" s="16" t="n"/>
+      <c r="M17" s="16" t="n"/>
+      <c r="N17" s="16" t="n"/>
+      <c r="O17" s="16" t="n"/>
+      <c r="P17" s="16" t="n"/>
+      <c r="Q17" s="16" t="n"/>
+      <c r="R17" s="16" t="n"/>
+      <c r="S17" s="16" t="n"/>
+      <c r="T17" s="16" t="n"/>
+      <c r="U17" s="16" t="n"/>
+      <c r="V17" s="32">
+        <f>SUM(C17:U17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="62" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>M5 x 35</t>
         </is>
       </c>
-      <c r="C18" s="47" t="n"/>
-      <c r="D18" s="47" t="n"/>
-      <c r="E18" s="47" t="n"/>
-      <c r="F18" s="47" t="n"/>
-      <c r="G18" s="47" t="n"/>
-      <c r="H18" s="47" t="n"/>
-      <c r="I18" s="47" t="n"/>
-      <c r="J18" s="47" t="n"/>
-      <c r="K18" s="47" t="n"/>
-      <c r="L18" s="47" t="n"/>
-      <c r="M18" s="47" t="n"/>
-      <c r="N18" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="O18" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="P18" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q18" s="47" t="n"/>
-      <c r="R18" s="47" t="n"/>
-      <c r="S18" s="47" t="n"/>
-      <c r="T18" s="47" t="n"/>
-      <c r="U18" s="63">
-        <f>SUM(C18:T18)</f>
+      <c r="C18" s="16" t="n"/>
+      <c r="D18" s="16" t="n"/>
+      <c r="E18" s="16" t="n"/>
+      <c r="F18" s="16" t="n"/>
+      <c r="G18" s="16" t="n"/>
+      <c r="H18" s="16" t="n"/>
+      <c r="I18" s="16" t="n"/>
+      <c r="J18" s="16" t="n"/>
+      <c r="K18" s="16" t="n"/>
+      <c r="L18" s="16" t="n"/>
+      <c r="M18" s="16" t="n"/>
+      <c r="N18" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="P18" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="16" t="n"/>
+      <c r="R18" s="16" t="n"/>
+      <c r="S18" s="16" t="n"/>
+      <c r="T18" s="16" t="n"/>
+      <c r="U18" s="16" t="n"/>
+      <c r="V18" s="32">
+        <f>SUM(C18:U18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="62" t="inlineStr">
+      <c r="B19" s="31" t="inlineStr">
         <is>
           <t>M5 x 45</t>
         </is>
       </c>
-      <c r="C19" s="47" t="n"/>
-      <c r="D19" s="47" t="n"/>
-      <c r="E19" s="47" t="n"/>
-      <c r="F19" s="47" t="n"/>
-      <c r="G19" s="47" t="n"/>
-      <c r="H19" s="47" t="n"/>
-      <c r="I19" s="47" t="n"/>
-      <c r="J19" s="47" t="n"/>
-      <c r="K19" s="47" t="n"/>
-      <c r="L19" s="47" t="n"/>
-      <c r="M19" s="47" t="n"/>
-      <c r="N19" s="47" t="n"/>
-      <c r="O19" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="P19" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q19" s="47" t="n"/>
-      <c r="R19" s="47" t="n"/>
-      <c r="S19" s="47" t="n"/>
-      <c r="T19" s="47" t="n"/>
-      <c r="U19" s="63">
-        <f>SUM(C19:T19)</f>
+      <c r="C19" s="16" t="n"/>
+      <c r="D19" s="16" t="n"/>
+      <c r="E19" s="16" t="n"/>
+      <c r="F19" s="16" t="n"/>
+      <c r="G19" s="16" t="n"/>
+      <c r="H19" s="16" t="n"/>
+      <c r="I19" s="16" t="n"/>
+      <c r="J19" s="16" t="n"/>
+      <c r="K19" s="16" t="n"/>
+      <c r="L19" s="16" t="n"/>
+      <c r="M19" s="16" t="n"/>
+      <c r="N19" s="16" t="n"/>
+      <c r="O19" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="P19" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" s="16" t="n"/>
+      <c r="R19" s="16" t="n"/>
+      <c r="S19" s="16" t="n"/>
+      <c r="T19" s="16" t="n"/>
+      <c r="U19" s="16" t="n"/>
+      <c r="V19" s="32">
+        <f>SUM(C19:U19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="62" t="inlineStr">
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>M5 x 55</t>
         </is>
       </c>
-      <c r="C20" s="47" t="n"/>
-      <c r="D20" s="47" t="n"/>
-      <c r="E20" s="47" t="n"/>
-      <c r="F20" s="47" t="n"/>
-      <c r="G20" s="47" t="n"/>
-      <c r="H20" s="47" t="n"/>
-      <c r="I20" s="47" t="n"/>
-      <c r="J20" s="47" t="n"/>
-      <c r="K20" s="47" t="n"/>
-      <c r="L20" s="47" t="n"/>
-      <c r="M20" s="47" t="n"/>
-      <c r="N20" s="47" t="n"/>
-      <c r="O20" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="P20" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q20" s="47" t="n"/>
-      <c r="R20" s="47" t="n"/>
-      <c r="S20" s="47" t="n"/>
-      <c r="T20" s="47" t="n"/>
-      <c r="U20" s="63">
-        <f>SUM(C20:T20)</f>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="16" t="n"/>
+      <c r="F20" s="16" t="n"/>
+      <c r="G20" s="16" t="n"/>
+      <c r="H20" s="16" t="n"/>
+      <c r="I20" s="16" t="n"/>
+      <c r="J20" s="16" t="n"/>
+      <c r="K20" s="16" t="n"/>
+      <c r="L20" s="16" t="n"/>
+      <c r="M20" s="16" t="n"/>
+      <c r="N20" s="16" t="n"/>
+      <c r="O20" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="P20" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" s="16" t="n"/>
+      <c r="R20" s="16" t="n"/>
+      <c r="S20" s="16" t="n"/>
+      <c r="T20" s="16" t="n"/>
+      <c r="U20" s="16" t="n"/>
+      <c r="V20" s="32">
+        <f>SUM(C20:U20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="15" t="n"/>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="16" t="n"/>
-      <c r="E21" s="16" t="n"/>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="16" t="n"/>
-      <c r="H21" s="16" t="n"/>
-      <c r="I21" s="16" t="n"/>
-      <c r="J21" s="16" t="n"/>
-      <c r="K21" s="16" t="n"/>
-      <c r="L21" s="16" t="n"/>
-      <c r="M21" s="16" t="n"/>
-      <c r="N21" s="16" t="n"/>
-      <c r="O21" s="16" t="n"/>
-      <c r="P21" s="16" t="n"/>
-      <c r="Q21" s="16" t="n"/>
-      <c r="R21" s="16" t="n"/>
-      <c r="S21" s="16" t="n"/>
-      <c r="T21" s="17" t="n"/>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="n"/>
+      <c r="P21" s="4" t="n"/>
+      <c r="Q21" s="4" t="n"/>
+      <c r="R21" s="4" t="n"/>
+      <c r="S21" s="4" t="n"/>
+      <c r="T21" s="4" t="n"/>
+      <c r="U21" s="4" t="n"/>
+      <c r="V21" s="4" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="62" t="inlineStr">
+      <c r="B22" s="45" t="inlineStr">
+        <is>
+          <t>UNC x 40</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="16" t="n"/>
+      <c r="F22" s="16" t="n"/>
+      <c r="G22" s="16" t="n"/>
+      <c r="H22" s="16" t="n"/>
+      <c r="I22" s="16" t="n"/>
+      <c r="J22" s="16" t="n"/>
+      <c r="K22" s="16" t="n"/>
+      <c r="L22" s="16" t="n"/>
+      <c r="M22" s="16" t="n"/>
+      <c r="N22" s="16" t="n"/>
+      <c r="O22" s="16" t="n"/>
+      <c r="P22" s="16" t="n"/>
+      <c r="Q22" s="16" t="n"/>
+      <c r="R22" s="16" t="n"/>
+      <c r="S22" s="16" t="n"/>
+      <c r="T22" s="16" t="n"/>
+      <c r="U22" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V22" s="32">
+        <f>SUM(C22:U22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n"/>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="4" t="n"/>
+      <c r="K23" s="4" t="n"/>
+      <c r="L23" s="4" t="n"/>
+      <c r="M23" s="4" t="n"/>
+      <c r="N23" s="4" t="n"/>
+      <c r="O23" s="4" t="n"/>
+      <c r="P23" s="4" t="n"/>
+      <c r="Q23" s="4" t="n"/>
+      <c r="R23" s="4" t="n"/>
+      <c r="S23" s="4" t="n"/>
+      <c r="T23" s="4" t="n"/>
+      <c r="U23" s="4" t="n"/>
+      <c r="V23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="31" t="inlineStr">
         <is>
           <t>M8 x 25</t>
         </is>
       </c>
-      <c r="C22" s="47" t="n"/>
-      <c r="D22" s="47" t="n"/>
-      <c r="E22" s="47" t="n"/>
-      <c r="F22" s="47" t="n"/>
-      <c r="G22" s="47" t="n"/>
-      <c r="H22" s="47" t="n"/>
-      <c r="I22" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="47" t="n"/>
-      <c r="K22" s="47" t="n"/>
-      <c r="L22" s="47" t="n"/>
-      <c r="M22" s="47" t="n"/>
-      <c r="N22" s="47" t="n"/>
-      <c r="O22" s="47" t="n"/>
-      <c r="P22" s="47" t="n"/>
-      <c r="Q22" s="47" t="n"/>
-      <c r="R22" s="47" t="n"/>
-      <c r="S22" s="47" t="n"/>
-      <c r="T22" s="47" t="n"/>
-      <c r="U22" s="63">
-        <f>SUM(C22:T22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="62" t="inlineStr">
-        <is>
-          <t>M8 x 45</t>
-        </is>
-      </c>
-      <c r="C23" s="47" t="n"/>
-      <c r="D23" s="47" t="n"/>
-      <c r="E23" s="47" t="n"/>
-      <c r="F23" s="47" t="n"/>
-      <c r="G23" s="47" t="n"/>
-      <c r="H23" s="47" t="n"/>
-      <c r="I23" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="47" t="n"/>
-      <c r="K23" s="47" t="n"/>
-      <c r="L23" s="47" t="n"/>
-      <c r="M23" s="47" t="n"/>
-      <c r="N23" s="47" t="n"/>
-      <c r="O23" s="47" t="n"/>
-      <c r="P23" s="47" t="n"/>
-      <c r="Q23" s="47" t="n"/>
-      <c r="R23" s="47" t="n"/>
-      <c r="S23" s="47" t="n"/>
-      <c r="T23" s="47" t="n"/>
-      <c r="U23" s="63">
-        <f>SUM(C23:T23)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="15" t="n"/>
       <c r="C24" s="16" t="n"/>
       <c r="D24" s="16" t="n"/>
       <c r="E24" s="16" t="n"/>
       <c r="F24" s="16" t="n"/>
       <c r="G24" s="16" t="n"/>
       <c r="H24" s="16" t="n"/>
-      <c r="I24" s="16" t="n"/>
+      <c r="I24" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="J24" s="16" t="n"/>
       <c r="K24" s="16" t="n"/>
       <c r="L24" s="16" t="n"/>
@@ -3823,231 +3855,235 @@
       <c r="Q24" s="16" t="n"/>
       <c r="R24" s="16" t="n"/>
       <c r="S24" s="16" t="n"/>
-      <c r="T24" s="17" t="n"/>
+      <c r="T24" s="16" t="n"/>
+      <c r="U24" s="16" t="n"/>
+      <c r="V24" s="32">
+        <f>SUM(C24:U24)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
-      <c r="B25" s="62" t="inlineStr">
+      <c r="B25" s="31" t="inlineStr">
+        <is>
+          <t>M8 x 45</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="16" t="n"/>
+      <c r="F25" s="16" t="n"/>
+      <c r="G25" s="16" t="n"/>
+      <c r="H25" s="16" t="n"/>
+      <c r="I25" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="16" t="n"/>
+      <c r="K25" s="16" t="n"/>
+      <c r="L25" s="16" t="n"/>
+      <c r="M25" s="16" t="n"/>
+      <c r="N25" s="16" t="n"/>
+      <c r="O25" s="16" t="n"/>
+      <c r="P25" s="16" t="n"/>
+      <c r="Q25" s="16" t="n"/>
+      <c r="R25" s="16" t="n"/>
+      <c r="S25" s="16" t="n"/>
+      <c r="T25" s="16" t="n"/>
+      <c r="U25" s="16" t="n"/>
+      <c r="V25" s="32">
+        <f>SUM(C25:U25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
+      <c r="K26" s="4" t="n"/>
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="4" t="n"/>
+      <c r="N26" s="4" t="n"/>
+      <c r="O26" s="4" t="n"/>
+      <c r="P26" s="4" t="n"/>
+      <c r="Q26" s="4" t="n"/>
+      <c r="R26" s="4" t="n"/>
+      <c r="S26" s="4" t="n"/>
+      <c r="T26" s="4" t="n"/>
+      <c r="U26" s="4" t="n"/>
+      <c r="V26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="31" t="inlineStr">
         <is>
           <t>M2.5 Insert</t>
         </is>
       </c>
-      <c r="C25" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="D25" s="47" t="n"/>
-      <c r="E25" s="47" t="n"/>
-      <c r="F25" s="47" t="n"/>
-      <c r="G25" s="47" t="n"/>
-      <c r="H25" s="47" t="n"/>
-      <c r="I25" s="47" t="n"/>
-      <c r="J25" s="47" t="n"/>
-      <c r="K25" s="47" t="n"/>
-      <c r="L25" s="47" t="n"/>
-      <c r="M25" s="47" t="n"/>
-      <c r="N25" s="47" t="n"/>
-      <c r="O25" s="47" t="n"/>
-      <c r="P25" s="47" t="n"/>
-      <c r="Q25" s="47" t="n"/>
-      <c r="R25" s="47" t="n"/>
-      <c r="S25" s="47" t="n"/>
-      <c r="T25" s="47" t="n"/>
-      <c r="U25" s="63">
-        <f>SUM(C25:T25)</f>
+      <c r="C27" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" s="16" t="n"/>
+      <c r="E27" s="16" t="n"/>
+      <c r="F27" s="16" t="n"/>
+      <c r="G27" s="16" t="n"/>
+      <c r="H27" s="16" t="n"/>
+      <c r="I27" s="16" t="n"/>
+      <c r="J27" s="16" t="n"/>
+      <c r="K27" s="16" t="n"/>
+      <c r="L27" s="16" t="n"/>
+      <c r="M27" s="16" t="n"/>
+      <c r="N27" s="16" t="n"/>
+      <c r="O27" s="16" t="n"/>
+      <c r="P27" s="16" t="n"/>
+      <c r="Q27" s="16" t="n"/>
+      <c r="R27" s="16" t="n"/>
+      <c r="S27" s="16" t="n"/>
+      <c r="T27" s="16" t="n"/>
+      <c r="U27" s="16" t="n"/>
+      <c r="V27" s="32">
+        <f>SUM(C27:U27)</f>
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="62" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="31" t="inlineStr">
         <is>
           <t>M3 Nyloc Nut</t>
         </is>
       </c>
-      <c r="C26" s="47" t="n"/>
-      <c r="D26" s="47" t="n"/>
-      <c r="E26" s="47" t="n"/>
-      <c r="F26" s="47" t="n"/>
-      <c r="G26" s="47" t="n"/>
-      <c r="H26" s="47" t="n"/>
-      <c r="I26" s="47" t="n"/>
-      <c r="J26" s="47" t="n"/>
-      <c r="K26" s="47" t="n"/>
-      <c r="L26" s="47" t="n"/>
-      <c r="M26" s="47" t="n">
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="16" t="n"/>
+      <c r="E28" s="16" t="n"/>
+      <c r="F28" s="16" t="n"/>
+      <c r="G28" s="16" t="n"/>
+      <c r="H28" s="16" t="n"/>
+      <c r="I28" s="16" t="n"/>
+      <c r="J28" s="16" t="n"/>
+      <c r="K28" s="16" t="n"/>
+      <c r="L28" s="16" t="n"/>
+      <c r="M28" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="N26" s="47" t="n"/>
-      <c r="O26" s="47" t="n"/>
-      <c r="P26" s="47" t="n"/>
-      <c r="Q26" s="47" t="n"/>
-      <c r="R26" s="47" t="n"/>
-      <c r="S26" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="U26" s="63">
-        <f>SUM(C26:T26)</f>
+      <c r="N28" s="16" t="n"/>
+      <c r="O28" s="16" t="n"/>
+      <c r="P28" s="16" t="n"/>
+      <c r="Q28" s="16" t="n"/>
+      <c r="R28" s="16" t="n"/>
+      <c r="S28" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" s="16" t="n"/>
+      <c r="V28" s="32">
+        <f>SUM(C28:U28)</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="62" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="31" t="inlineStr">
         <is>
           <t>M3 Insert</t>
         </is>
       </c>
-      <c r="C27" s="47" t="n">
+      <c r="C29" s="16" t="n">
         <v>16</v>
       </c>
-      <c r="D27" s="47" t="n">
+      <c r="D29" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="E27" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="F27" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="G27" s="47" t="n"/>
-      <c r="H27" s="47" t="n"/>
-      <c r="I27" s="47" t="n"/>
-      <c r="J27" s="47" t="n"/>
-      <c r="K27" s="47" t="n"/>
-      <c r="L27" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="M27" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="N27" s="47" t="n"/>
-      <c r="O27" s="47" t="n"/>
-      <c r="P27" s="47" t="n"/>
-      <c r="Q27" s="47" t="n"/>
-      <c r="R27" s="47" t="n"/>
-      <c r="S27" s="47" t="n"/>
-      <c r="T27" s="47" t="n"/>
-      <c r="U27" s="63">
-        <f>SUM(C27:T27)</f>
+      <c r="E29" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G29" s="16" t="n"/>
+      <c r="H29" s="16" t="n"/>
+      <c r="I29" s="16" t="n"/>
+      <c r="J29" s="16" t="n"/>
+      <c r="K29" s="16" t="n"/>
+      <c r="L29" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="M29" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="N29" s="16" t="n"/>
+      <c r="O29" s="16" t="n"/>
+      <c r="P29" s="16" t="n"/>
+      <c r="Q29" s="16" t="n"/>
+      <c r="R29" s="16" t="n"/>
+      <c r="S29" s="16" t="n"/>
+      <c r="T29" s="16" t="n"/>
+      <c r="U29" s="16" t="n"/>
+      <c r="V29" s="32">
+        <f>SUM(C29:U29)</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="62" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="31" t="inlineStr">
         <is>
           <t>M5 Nyloc Nut</t>
         </is>
       </c>
-      <c r="C28" s="47" t="n"/>
-      <c r="D28" s="47" t="n"/>
-      <c r="E28" s="47" t="n"/>
-      <c r="F28" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="G28" s="47" t="n"/>
-      <c r="H28" s="47" t="n"/>
-      <c r="I28" s="47" t="n"/>
-      <c r="J28" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="K28" s="47" t="n"/>
-      <c r="L28" s="47" t="n"/>
-      <c r="M28" s="47" t="n"/>
-      <c r="N28" s="47" t="n"/>
-      <c r="O28" s="47" t="n">
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="16" t="n"/>
+      <c r="E30" s="16" t="n"/>
+      <c r="F30" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" s="16" t="n"/>
+      <c r="H30" s="16" t="n"/>
+      <c r="I30" s="16" t="n"/>
+      <c r="J30" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K30" s="16" t="n"/>
+      <c r="L30" s="16" t="n"/>
+      <c r="M30" s="16" t="n"/>
+      <c r="N30" s="16" t="n"/>
+      <c r="O30" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="P28" s="47" t="n">
+      <c r="P30" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="Q28" s="47" t="n">
+      <c r="Q30" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="S28" s="47" t="n"/>
-      <c r="T28" s="47" t="n"/>
-      <c r="U28" s="63">
-        <f>SUM(C28:T28)</f>
+      <c r="R30" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="S30" s="16" t="n"/>
+      <c r="T30" s="16" t="n"/>
+      <c r="U30" s="16" t="n"/>
+      <c r="V30" s="32">
+        <f>SUM(C30:U30)</f>
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="62" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="31" t="inlineStr">
         <is>
           <t>M8 Domed Nut</t>
         </is>
       </c>
-      <c r="C29" s="47" t="n"/>
-      <c r="D29" s="47" t="n"/>
-      <c r="E29" s="47" t="n"/>
-      <c r="F29" s="47" t="n"/>
-      <c r="G29" s="47" t="n"/>
-      <c r="H29" s="47" t="n"/>
-      <c r="I29" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="J29" s="47" t="n"/>
-      <c r="K29" s="47" t="n"/>
-      <c r="L29" s="47" t="n"/>
-      <c r="M29" s="47" t="n"/>
-      <c r="N29" s="47" t="n"/>
-      <c r="O29" s="47" t="n"/>
-      <c r="P29" s="47" t="n"/>
-      <c r="Q29" s="47" t="n"/>
-      <c r="R29" s="47" t="n"/>
-      <c r="S29" s="47" t="n"/>
-      <c r="T29" s="47" t="n"/>
-      <c r="U29" s="63">
-        <f>SUM(C29:T29)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="62" t="inlineStr">
-        <is>
-          <t>3/8 UNC Insert</t>
-        </is>
-      </c>
-      <c r="C30" s="47" t="n"/>
-      <c r="D30" s="47" t="n"/>
-      <c r="E30" s="47" t="n"/>
-      <c r="F30" s="47" t="n"/>
-      <c r="G30" s="47" t="n"/>
-      <c r="H30" s="47" t="n"/>
-      <c r="I30" s="47" t="n"/>
-      <c r="J30" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" s="47" t="n"/>
-      <c r="L30" s="47" t="n"/>
-      <c r="M30" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" s="47" t="n"/>
-      <c r="P30" s="47" t="n"/>
-      <c r="Q30" s="47" t="n"/>
-      <c r="R30" s="47" t="n"/>
-      <c r="S30" s="47" t="n"/>
-      <c r="T30" s="47" t="n"/>
-      <c r="U30" s="63">
-        <f>SUM(C30:T30)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="15" t="n"/>
       <c r="C31" s="16" t="n"/>
       <c r="D31" s="16" t="n"/>
       <c r="E31" s="16" t="n"/>
       <c r="F31" s="16" t="n"/>
       <c r="G31" s="16" t="n"/>
       <c r="H31" s="16" t="n"/>
-      <c r="I31" s="16" t="n"/>
+      <c r="I31" s="16" t="n">
+        <v>2</v>
+      </c>
       <c r="J31" s="16" t="n"/>
       <c r="K31" s="16" t="n"/>
       <c r="L31" s="16" t="n"/>
@@ -4058,83 +4094,151 @@
       <c r="Q31" s="16" t="n"/>
       <c r="R31" s="16" t="n"/>
       <c r="S31" s="16" t="n"/>
-      <c r="T31" s="17" t="n"/>
+      <c r="T31" s="16" t="n"/>
+      <c r="U31" s="16" t="n"/>
+      <c r="V31" s="32">
+        <f>SUM(C31:U31)</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
-      <c r="B32" s="62" t="inlineStr">
+      <c r="B32" s="31" t="inlineStr">
+        <is>
+          <t>3/8 UNC Insert</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="16" t="n"/>
+      <c r="E32" s="16" t="n"/>
+      <c r="F32" s="16" t="n"/>
+      <c r="G32" s="16" t="n"/>
+      <c r="H32" s="16" t="n"/>
+      <c r="I32" s="16" t="n"/>
+      <c r="J32" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" s="16" t="n"/>
+      <c r="L32" s="16" t="n"/>
+      <c r="M32" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" s="16" t="n"/>
+      <c r="P32" s="16" t="n"/>
+      <c r="Q32" s="16" t="n"/>
+      <c r="R32" s="16" t="n"/>
+      <c r="S32" s="16" t="n"/>
+      <c r="T32" s="16" t="n"/>
+      <c r="U32" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V32" s="32">
+        <f>SUM(C32:U32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n"/>
+      <c r="P33" s="4" t="n"/>
+      <c r="Q33" s="4" t="n"/>
+      <c r="R33" s="4" t="n"/>
+      <c r="S33" s="4" t="n"/>
+      <c r="T33" s="4" t="n"/>
+      <c r="U33" s="4" t="n"/>
+      <c r="V33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="31" t="inlineStr">
         <is>
           <t>M3 Washer</t>
         </is>
       </c>
-      <c r="C32" s="47" t="n">
+      <c r="C34" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="D32" s="47" t="n"/>
-      <c r="E32" s="47" t="n">
+      <c r="D34" s="16" t="n"/>
+      <c r="E34" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="F32" s="47" t="n"/>
-      <c r="G32" s="47" t="n">
+      <c r="F34" s="16" t="n"/>
+      <c r="G34" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="H32" s="47" t="n">
+      <c r="H34" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="I32" s="47" t="n"/>
-      <c r="J32" s="47" t="n"/>
-      <c r="K32" s="47" t="n"/>
-      <c r="L32" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="M32" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="N32" s="47" t="n"/>
-      <c r="O32" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="P32" s="47" t="n"/>
-      <c r="Q32" s="47" t="n"/>
-      <c r="R32" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="S32" s="47" t="n"/>
-      <c r="T32" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="U32" s="63">
-        <f>SUM(C32:T32)</f>
+      <c r="I34" s="16" t="n"/>
+      <c r="J34" s="16" t="n"/>
+      <c r="K34" s="16" t="n"/>
+      <c r="L34" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="M34" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="N34" s="16" t="n"/>
+      <c r="O34" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="P34" s="16" t="n"/>
+      <c r="Q34" s="16" t="n"/>
+      <c r="R34" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="S34" s="16" t="n"/>
+      <c r="T34" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" s="16" t="n"/>
+      <c r="V34" s="32">
+        <f>SUM(C34:U34)</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="62" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="31" t="inlineStr">
         <is>
           <t>M5 Washer</t>
         </is>
       </c>
-      <c r="C33" s="47" t="n"/>
-      <c r="D33" s="47" t="n"/>
-      <c r="E33" s="47" t="n"/>
-      <c r="F33" s="47" t="n"/>
-      <c r="G33" s="47" t="n"/>
-      <c r="H33" s="47" t="n"/>
-      <c r="I33" s="47" t="n"/>
-      <c r="J33" s="47" t="n"/>
-      <c r="K33" s="47" t="n"/>
-      <c r="L33" s="47" t="n"/>
-      <c r="M33" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="N33" s="47" t="n"/>
-      <c r="O33" s="47" t="n"/>
-      <c r="P33" s="47" t="n"/>
-      <c r="Q33" s="47" t="n"/>
-      <c r="R33" s="47" t="n"/>
-      <c r="S33" s="47" t="n"/>
-      <c r="T33" s="47" t="n"/>
-      <c r="U33" s="63">
-        <f>SUM(C33:T33)</f>
+      <c r="C35" s="16" t="n"/>
+      <c r="D35" s="16" t="n"/>
+      <c r="E35" s="16" t="n"/>
+      <c r="F35" s="16" t="n"/>
+      <c r="G35" s="16" t="n"/>
+      <c r="H35" s="16" t="n"/>
+      <c r="I35" s="16" t="n"/>
+      <c r="J35" s="16" t="n"/>
+      <c r="K35" s="16" t="n"/>
+      <c r="L35" s="16" t="n"/>
+      <c r="M35" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="N35" s="16" t="n"/>
+      <c r="O35" s="16" t="n"/>
+      <c r="P35" s="16" t="n"/>
+      <c r="Q35" s="16" t="n"/>
+      <c r="R35" s="16" t="n"/>
+      <c r="S35" s="16" t="n"/>
+      <c r="T35" s="16" t="n"/>
+      <c r="U35" s="16" t="n"/>
+      <c r="V35" s="32">
+        <f>SUM(C35:U35)</f>
         <v/>
       </c>
     </row>

--- a/docs/assets/BoM.xlsx
+++ b/docs/assets/BoM.xlsx
@@ -1907,7 +1907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:AN57"/>
+  <dimension ref="A1:AN57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="10.83203125" customWidth="1" style="41" min="1" max="1"/>
@@ -1949,6 +1949,7 @@
     <col width="10.83203125" customWidth="1" style="41" min="40" max="16384"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="18" t="inlineStr">
         <is>
@@ -2157,7 +2158,7 @@
       </c>
       <c r="AD4" s="38" t="inlineStr">
         <is>
-          <t>3/8 UNC Insert</t>
+          <t>1/4 UNC Insert</t>
         </is>
       </c>
       <c r="AE4" s="40" t="n">
@@ -2469,6 +2470,10 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
     <row r="20">
       <c r="B20" s="18" t="inlineStr">
         <is>
@@ -2528,7 +2533,7 @@
       <c r="D21" s="2" t="n"/>
       <c r="F21" s="19" t="inlineStr">
         <is>
-          <t>3/8 UNC Insert</t>
+          <t>1/4 UNC Insert</t>
         </is>
       </c>
       <c r="G21" s="20" t="n">
@@ -2591,7 +2596,7 @@
       <c r="AF21" s="2" t="n"/>
       <c r="AH21" s="39" t="inlineStr">
         <is>
-          <t>3/8 UNC Insert</t>
+          <t>1/4 UNC Insert</t>
         </is>
       </c>
       <c r="AI21" s="20" t="n">
@@ -2629,7 +2634,7 @@
     <row r="23">
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>3/8 UNC Insert</t>
+          <t>1/4 UNC Insert</t>
         </is>
       </c>
       <c r="C23" s="40" t="n">
@@ -2709,7 +2714,7 @@
       <c r="AF23" s="10" t="n"/>
       <c r="AH23" s="43" t="inlineStr">
         <is>
-          <t>3/4 UNC 40mm</t>
+          <t>1/4 UNC x 1½"</t>
         </is>
       </c>
       <c r="AI23" s="28" t="n">
@@ -3036,7 +3041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:V35"/>
+  <dimension ref="A1:V35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="3.33203125" customWidth="1" min="1" max="1"/>
@@ -3045,6 +3050,7 @@
     <col width="8" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="57" customHeight="1">
       <c r="B2" s="30" t="inlineStr">
         <is>
@@ -3778,7 +3784,7 @@
     <row r="22">
       <c r="B22" s="45" t="inlineStr">
         <is>
-          <t>UNC x 40</t>
+          <t>1/4 UNC x 1½"</t>
         </is>
       </c>
       <c r="C22" s="16" t="n"/>
@@ -4104,7 +4110,7 @@
     <row r="32">
       <c r="B32" s="31" t="inlineStr">
         <is>
-          <t>3/8 UNC Insert</t>
+          <t>1/4 UNC Insert</t>
         </is>
       </c>
       <c r="C32" s="16" t="n"/>

--- a/docs/assets/BoM.xlsx
+++ b/docs/assets/BoM.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="21">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -117,8 +117,31 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00808080"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -146,8 +169,18 @@
         <fgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F5597"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -331,11 +364,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -405,6 +452,28 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -803,8 +872,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C72"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <dimension ref="A1:C75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
@@ -812,1010 +881,1055 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="46" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="47" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="47" t="inlineStr">
         <is>
           <t>Buy</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="33" t="inlineStr">
+      <c r="A2" s="48" t="inlineStr">
         <is>
           <t>Circuit</t>
         </is>
       </c>
-      <c r="B2" s="34" t="n"/>
-      <c r="C2" s="35" t="n"/>
+      <c r="B2" s="49" t="n"/>
+      <c r="C2" s="49" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="50" t="inlineStr">
         <is>
           <t>Teensy 4.1</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="17" t="inlineStr">
+      <c r="B3" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="52" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>TMC2209</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="B4" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="52" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>5V regulator</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="B5" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="52" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="50" t="inlineStr">
         <is>
           <t>1n4007</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="B6" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="52" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="50" t="inlineStr">
         <is>
           <t>100nf 35v</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="51" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="52" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="50" t="inlineStr">
         <is>
           <t>1K ¼W</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="B8" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="52" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="50" t="inlineStr">
         <is>
           <t>100K ¼W</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="B9" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="52" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="50" t="inlineStr">
         <is>
           <t>Screw PCB terminals 5.08mm 2pin</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="B10" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="52" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="50" t="inlineStr">
         <is>
           <t>JST 4pin Plug + Lead + Socket</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="51" t="n">
         <v>6</v>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="52" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="50" t="inlineStr">
         <is>
           <t>JST 5pin Plug + Lead + Socket</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="B12" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="52" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="50" t="inlineStr">
         <is>
           <t>JST 2pin Plug + Lead + Socket</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="B13" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="52" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="50" t="inlineStr">
         <is>
           <t>Header Sockets</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="51" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="52" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="50" t="inlineStr">
         <is>
           <t>Header Pins</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="51" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="52" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="33" t="inlineStr">
+      <c r="A16" s="48" t="inlineStr">
         <is>
           <t>Mount</t>
         </is>
       </c>
-      <c r="B16" s="34" t="n"/>
-      <c r="C16" s="35" t="n"/>
+      <c r="B16" s="49" t="n"/>
+      <c r="C16" s="49" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="50" t="inlineStr">
         <is>
           <t>6824ZZ 120x150x16mm Bearing</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="B17" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="52" t="inlineStr">
         <is>
           <t>Simply Bearings</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="50" t="inlineStr">
         <is>
           <t>F688ZZ Flanged Bearing 8 x 16 x 5mm</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="B18" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" s="52" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="50" t="inlineStr">
         <is>
           <t>GT2 Pulley - 120 tooth, 8mm bore</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="B19" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="52" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="50" t="inlineStr">
         <is>
           <t>GT2 Pulley - 36 tooth, 5mm bore</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="B20" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="52" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="50" t="inlineStr">
         <is>
           <t>GT2 Pulley - 16 tooth, 5mm bore</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="B21" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="52" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="50" t="inlineStr">
         <is>
           <t>GT2 Belt - 580mm loop, 6mm wide</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="B22" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="52" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="50" t="inlineStr">
         <is>
           <t>GT2 Belt - 350mm loop, 6mm wide</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="B23" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="52" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="50" t="inlineStr">
         <is>
           <t>Nema14 0.9 deg 36Ncm</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="B24" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="52" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="50" t="inlineStr">
         <is>
           <t>Nema14 Round Pancake Stepper Motor 0.9 deg</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
+      <c r="B25" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="52" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="50" t="inlineStr">
         <is>
           <t>GX12 2 Pin Aviation Connector &amp; Panel Socket</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="B26" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="52" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="50" t="inlineStr">
         <is>
           <t>Waveshare ESP32-S3 1.75inch AMOLED Round Touch Display</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="B27" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="52" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="50" t="inlineStr">
         <is>
           <t>Sticky Pads Heavy Duty 40x40mm</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
+      <c r="B28" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="52" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="50" t="inlineStr">
         <is>
           <t>2.4GHz Antenna</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
+      <c r="B29" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="52" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="50" t="inlineStr">
         <is>
           <t>U.FL Mini PCI to SMA Female 20cm Lead</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
+      <c r="B30" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="52" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="33" t="inlineStr">
+      <c r="A31" s="50" t="inlineStr">
+        <is>
+          <t>1/4 UNC Insert</t>
+        </is>
+      </c>
+      <c r="B31" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="48" t="inlineStr">
         <is>
           <t>Mount - HDMI</t>
         </is>
       </c>
-      <c r="B31" s="34" t="n"/>
-      <c r="C31" s="35" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="B32" s="49" t="n"/>
+      <c r="C32" s="49" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="50" t="inlineStr">
         <is>
           <t>HDMI Keystone coupler</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="B33" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="50" t="inlineStr">
         <is>
           <t>HDMI Cable - 1m</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="33" t="inlineStr">
+      <c r="B34" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="48" t="inlineStr">
         <is>
           <t>Mount - SDI</t>
         </is>
       </c>
-      <c r="B34" s="34" t="n"/>
-      <c r="C34" s="35" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="B35" s="49" t="n"/>
+      <c r="C35" s="49" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="50" t="inlineStr">
         <is>
           <t>SDI Panel mount coupler</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="B36" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="50" t="inlineStr">
         <is>
           <t>HD-SDI Cable - 1m</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="33" t="inlineStr">
+      <c r="B37" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="48" t="inlineStr">
         <is>
           <t>Mount - BMD Converter</t>
         </is>
       </c>
-      <c r="B37" s="34" t="n"/>
-      <c r="C37" s="35" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="B38" s="49" t="n"/>
+      <c r="C38" s="49" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="50" t="inlineStr">
         <is>
           <t>Blackmagic Design Bi-Directional SDI/HDMI 3G</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="17" t="inlineStr">
+      <c r="B39" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="52" t="inlineStr">
         <is>
           <t>Thomann</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="50" t="inlineStr">
         <is>
           <t>SDI Panel mount coupler</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C39" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="B40" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="50" t="inlineStr">
         <is>
           <t>HD-SDI Cable - 1m, Right angle</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C40" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="B41" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="50" t="inlineStr">
         <is>
           <t>USB-C Cable - 1 Metre (cut and soldered to JST 2pin)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="33" t="inlineStr">
+      <c r="B42" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="48" t="inlineStr">
         <is>
           <t>Slider</t>
         </is>
       </c>
-      <c r="B42" s="34" t="n"/>
-      <c r="C42" s="35" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="B43" s="49" t="n"/>
+      <c r="C43" s="49" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="50" t="inlineStr">
         <is>
           <t>Aluminium Extrusion - 8040 C</t>
         </is>
       </c>
-      <c r="B43" s="16" t="inlineStr">
+      <c r="B44" s="51" t="inlineStr">
         <is>
           <t>1000 - 3000mm</t>
         </is>
       </c>
-      <c r="C43" s="17" t="inlineStr">
+      <c r="C44" s="52" t="inlineStr">
         <is>
           <t>Ooznest</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="50" t="inlineStr">
         <is>
           <t>GT2 Pulley - 36 tooth</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="B45" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="50" t="inlineStr">
         <is>
           <t>GT2 Belt - 5m</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+      <c r="B46" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="50" t="inlineStr">
         <is>
           <t>Idler - 6mm width, 3mm bore, 13mm diameter</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C46" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="B47" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="50" t="inlineStr">
         <is>
           <t>Nema14 1.8 deg 65Ncm</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="B48" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="50" t="inlineStr">
         <is>
           <t>V Slot Pulley Wheels 625zz</t>
         </is>
       </c>
-      <c r="B48" s="16" t="n">
+      <c r="B49" s="51" t="n">
         <v>16</v>
       </c>
-      <c r="C48" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="C49" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="50" t="inlineStr">
         <is>
           <t>XT60 Plug Connector Female and Male</t>
         </is>
       </c>
-      <c r="B49" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="15" t="inlineStr">
+      <c r="B50" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="50" t="inlineStr">
         <is>
           <t>GX12 2 Pin Aviation Connector &amp; Panel Socket</t>
         </is>
       </c>
-      <c r="B50" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="15" t="inlineStr">
+      <c r="B51" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="50" t="inlineStr">
         <is>
           <t>GX12 4 Pin Aviation Connector &amp; Panel Socket</t>
         </is>
       </c>
-      <c r="B51" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="33" t="inlineStr">
+      <c r="B52" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="50" t="inlineStr">
+        <is>
+          <t>1/4 UNC Insert</t>
+        </is>
+      </c>
+      <c r="B53" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="C53" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="50" t="inlineStr">
+        <is>
+          <t>1/4 UNC x 1½"</t>
+        </is>
+      </c>
+      <c r="B54" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" s="53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="48" t="inlineStr">
         <is>
           <t>Slider - HDMI</t>
         </is>
       </c>
-      <c r="B52" s="34" t="n"/>
-      <c r="C52" s="35" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="B55" s="49" t="n"/>
+      <c r="C55" s="49" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="50" t="inlineStr">
         <is>
           <t>HDMI Keystone coupler</t>
         </is>
       </c>
-      <c r="B53" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="15" t="inlineStr">
+      <c r="B56" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="50" t="inlineStr">
         <is>
           <t>HDMI Cable, 2m - 4m</t>
         </is>
       </c>
-      <c r="B54" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="33" t="inlineStr">
+      <c r="B57" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="48" t="inlineStr">
         <is>
           <t>Slider - SDI</t>
         </is>
       </c>
-      <c r="B55" s="34" t="n"/>
-      <c r="C55" s="35" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="15" t="inlineStr">
+      <c r="B58" s="49" t="n"/>
+      <c r="C58" s="49" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="50" t="inlineStr">
         <is>
           <t>SDI Panel mount coupler</t>
         </is>
       </c>
-      <c r="B56" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="15" t="inlineStr">
+      <c r="B59" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="50" t="inlineStr">
         <is>
           <t>HD-SDI Cable, 1m - 4m</t>
         </is>
       </c>
-      <c r="B57" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="33" t="inlineStr">
+      <c r="B60" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="48" t="inlineStr">
         <is>
           <t>Slider - BMD Converter</t>
         </is>
       </c>
-      <c r="B58" s="34" t="n"/>
-      <c r="C58" s="35" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="15" t="inlineStr">
+      <c r="B61" s="49" t="n"/>
+      <c r="C61" s="49" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="50" t="inlineStr">
         <is>
           <t>SDI Panel mount coupler</t>
         </is>
       </c>
-      <c r="B59" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C59" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="15" t="inlineStr">
+      <c r="B62" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C62" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="50" t="inlineStr">
         <is>
           <t>HD-SDI Cable, 2m - 4m</t>
         </is>
       </c>
-      <c r="B60" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C60" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="33" t="inlineStr">
+      <c r="B63" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="48" t="inlineStr">
         <is>
           <t>Hub</t>
         </is>
       </c>
-      <c r="B61" s="34" t="n"/>
-      <c r="C61" s="35" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="15" t="inlineStr">
+      <c r="B64" s="49" t="n"/>
+      <c r="C64" s="49" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="50" t="inlineStr">
         <is>
           <t>Seeed Studio XIAO ESP32S3</t>
         </is>
       </c>
-      <c r="B62" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C62" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="33" t="inlineStr">
+      <c r="B65" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="48" t="inlineStr">
         <is>
           <t>Hub Display</t>
         </is>
       </c>
-      <c r="B63" s="34" t="n"/>
-      <c r="C63" s="35" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="15" t="inlineStr">
+      <c r="B66" s="49" t="n"/>
+      <c r="C66" s="49" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="50" t="inlineStr">
         <is>
           <t>Waveshare ESP32-S3 7inch Capacitive Touch LCD</t>
         </is>
       </c>
-      <c r="B64" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C64" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="15" t="inlineStr">
+      <c r="B67" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="50" t="inlineStr">
         <is>
           <t>2.4GHz Antenna</t>
         </is>
       </c>
-      <c r="B65" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C65" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="15" t="inlineStr">
+      <c r="B68" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="50" t="inlineStr">
         <is>
           <t>U.FL Mini PCI to SMA Female 20cm Lead</t>
         </is>
       </c>
-      <c r="B66" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C66" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="15" t="inlineStr">
+      <c r="B69" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="50" t="inlineStr">
         <is>
           <t>USB-C Screw Hole Panel Mount</t>
         </is>
       </c>
-      <c r="B67" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C67" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="33" t="inlineStr">
+      <c r="B70" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="48" t="inlineStr">
         <is>
           <t>Misc</t>
         </is>
       </c>
-      <c r="B68" s="34" t="n"/>
-      <c r="C68" s="35" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="15" t="inlineStr">
+      <c r="B71" s="49" t="n"/>
+      <c r="C71" s="49" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="50" t="inlineStr">
         <is>
           <t>2 Core Wire - 30m, 20awg</t>
         </is>
       </c>
-      <c r="B69" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C69" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="15" t="inlineStr">
+      <c r="B72" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="50" t="inlineStr">
         <is>
           <t>4 Core Wire - 10m, 24awg</t>
         </is>
       </c>
-      <c r="B70" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C70" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="33" t="inlineStr">
+      <c r="B73" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" s="52" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="48" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="B71" s="34" t="n"/>
-      <c r="C71" s="35" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="15" t="inlineStr">
+      <c r="B74" s="49" t="n"/>
+      <c r="C74" s="49" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="50" t="inlineStr">
         <is>
           <t>UGREEN Video Capture Card HDMI to USB C 1080P 60FPS Capture (CV Tracking)</t>
         </is>
       </c>
-      <c r="B72" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C72" s="17" t="inlineStr">
+      <c r="B75" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" s="52" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
@@ -1823,19 +1937,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A63:C63"/>
     <mergeCell ref="A71:C71"/>
-    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A66:C66"/>
+    <mergeCell ref="A32:C32"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A31:C31"/>
     <mergeCell ref="A61:C61"/>
     <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A74:C74"/>
     <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A38:C38"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A64:C64"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
@@ -1865,15 +1979,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId39"/>
@@ -1882,20 +1996,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1907,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN57"/>
+  <dimension ref="B2:AN57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="10.83203125" customWidth="1" style="41" min="1" max="1"/>
@@ -1949,7 +2065,6 @@
     <col width="10.83203125" customWidth="1" style="41" min="40" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="18" t="inlineStr">
         <is>
@@ -2470,10 +2585,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
     <row r="20">
       <c r="B20" s="18" t="inlineStr">
         <is>
@@ -3041,7 +3152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V35"/>
+  <dimension ref="B2:V35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="3.33203125" customWidth="1" min="1" max="1"/>
@@ -3050,7 +3161,6 @@
     <col width="8" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="57" customHeight="1">
       <c r="B2" s="30" t="inlineStr">
         <is>

--- a/docs/assets/BoM.xlsx
+++ b/docs/assets/BoM.xlsx
@@ -180,7 +180,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -378,11 +378,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -475,6 +519,8 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -903,8 +949,8 @@
           <t>Circuit</t>
         </is>
       </c>
-      <c r="B2" s="49" t="n"/>
-      <c r="C2" s="49" t="n"/>
+      <c r="B2" s="54" t="n"/>
+      <c r="C2" s="55" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="50" t="inlineStr">
@@ -1111,8 +1157,8 @@
           <t>Mount</t>
         </is>
       </c>
-      <c r="B16" s="49" t="n"/>
-      <c r="C16" s="49" t="n"/>
+      <c r="B16" s="54" t="n"/>
+      <c r="C16" s="55" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="50" t="inlineStr">
@@ -1345,8 +1391,8 @@
           <t>Mount - HDMI</t>
         </is>
       </c>
-      <c r="B32" s="49" t="n"/>
-      <c r="C32" s="49" t="n"/>
+      <c r="B32" s="54" t="n"/>
+      <c r="C32" s="55" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="50" t="inlineStr">
@@ -1384,8 +1430,8 @@
           <t>Mount - SDI</t>
         </is>
       </c>
-      <c r="B35" s="49" t="n"/>
-      <c r="C35" s="49" t="n"/>
+      <c r="B35" s="54" t="n"/>
+      <c r="C35" s="55" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="50" t="inlineStr">
@@ -1423,8 +1469,8 @@
           <t>Mount - BMD Converter</t>
         </is>
       </c>
-      <c r="B38" s="49" t="n"/>
-      <c r="C38" s="49" t="n"/>
+      <c r="B38" s="54" t="n"/>
+      <c r="C38" s="55" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="50" t="inlineStr">
@@ -1492,8 +1538,8 @@
           <t>Slider</t>
         </is>
       </c>
-      <c r="B43" s="49" t="n"/>
-      <c r="C43" s="49" t="n"/>
+      <c r="B43" s="54" t="n"/>
+      <c r="C43" s="55" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="50" t="inlineStr">
@@ -1668,8 +1714,8 @@
           <t>Slider - HDMI</t>
         </is>
       </c>
-      <c r="B55" s="49" t="n"/>
-      <c r="C55" s="49" t="n"/>
+      <c r="B55" s="54" t="n"/>
+      <c r="C55" s="55" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="50" t="inlineStr">
@@ -1707,8 +1753,8 @@
           <t>Slider - SDI</t>
         </is>
       </c>
-      <c r="B58" s="49" t="n"/>
-      <c r="C58" s="49" t="n"/>
+      <c r="B58" s="54" t="n"/>
+      <c r="C58" s="55" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="50" t="inlineStr">
@@ -1746,8 +1792,8 @@
           <t>Slider - BMD Converter</t>
         </is>
       </c>
-      <c r="B61" s="49" t="n"/>
-      <c r="C61" s="49" t="n"/>
+      <c r="B61" s="54" t="n"/>
+      <c r="C61" s="55" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="50" t="inlineStr">
@@ -1785,8 +1831,8 @@
           <t>Hub</t>
         </is>
       </c>
-      <c r="B64" s="49" t="n"/>
-      <c r="C64" s="49" t="n"/>
+      <c r="B64" s="54" t="n"/>
+      <c r="C64" s="55" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="50" t="inlineStr">
@@ -1809,8 +1855,8 @@
           <t>Hub Display</t>
         </is>
       </c>
-      <c r="B66" s="49" t="n"/>
-      <c r="C66" s="49" t="n"/>
+      <c r="B66" s="54" t="n"/>
+      <c r="C66" s="55" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="50" t="inlineStr">
@@ -1878,8 +1924,8 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="B71" s="49" t="n"/>
-      <c r="C71" s="49" t="n"/>
+      <c r="B71" s="54" t="n"/>
+      <c r="C71" s="55" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="50" t="inlineStr">
@@ -1917,8 +1963,8 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="B74" s="49" t="n"/>
-      <c r="C74" s="49" t="n"/>
+      <c r="B74" s="54" t="n"/>
+      <c r="C74" s="55" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="50" t="inlineStr">
